--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,6 +772,878 @@
         <is>
           <t>Odd_Corners_Under115</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>7954031</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>45892.59375</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Hapoel Katamon</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ashdod</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>['38']</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>['54', '74']</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>7954032</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>45892.59375</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hapoel Tel Aviv</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Ironi Kiryat Shmona</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>['58', '73']</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>7954030</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>45892.60416666666</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ironi Tiberias</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Hapoel Haifa</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>['54']</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>7954033</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>45892.60416666666</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Maccabi Haifa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Maccabi Bnei Raina</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>['28', '51', '69', '77']</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP5"/>
+  <dimension ref="A1:BP6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -926,22 +926,22 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX2" t="n">
         <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
         <v>3</v>
@@ -1144,13 +1144,13 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX3" t="n">
         <v>5</v>
@@ -1159,7 +1159,7 @@
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA3" t="n">
         <v>6</v>
@@ -1368,13 +1368,13 @@
         <v>2</v>
       </c>
       <c r="AW4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX4" t="n">
         <v>8</v>
       </c>
       <c r="AY4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ4" t="n">
         <v>10</v>
@@ -1580,19 +1580,19 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AV5" t="n">
         <v>2</v>
       </c>
       <c r="AW5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX5" t="n">
         <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ5" t="n">
         <v>6</v>
@@ -1644,6 +1644,224 @@
       </c>
       <c r="BP5" t="n">
         <v>1.12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>7954029</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>45893.59375</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Maccabi Netanya</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Hapoel Be'er Sheva</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>['9', '20']</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>['33', '43', '45+3', '63']</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP6"/>
+  <dimension ref="A1:BP7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1862,6 +1862,224 @@
       </c>
       <c r="BP6" t="n">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>7954035</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>45894.58333333334</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bnei Sakhnin</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Beitar Jerusalem</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>['18', '45+4']</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -779,7 +779,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>7954031</v>
+        <v>8237909</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -799,197 +799,197 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
         <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2</v>
       </c>
       <c r="N2" t="n">
         <v>3</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>['58', '73']</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>['54', '74']</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="Q2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH2" t="n">
         <v>2.88</v>
       </c>
-      <c r="R2" t="n">
+      <c r="BI2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>2.1</v>
       </c>
-      <c r="S2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BI2" t="n">
+      <c r="BK2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BL2" t="n">
         <v>1.72</v>
       </c>
-      <c r="BJ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BM2" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.13</v>
+        <v>4.15</v>
       </c>
       <c r="BP2" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="3">
@@ -997,7 +997,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>7954032</v>
+        <v>8237910</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1017,110 +1017,110 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
         <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>['58', '73']</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>['54', '74']</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>3.1</v>
+        <v>2.64</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="U3" t="n">
         <v>2.75</v>
       </c>
       <c r="V3" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>6.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.6</v>
+        <v>2.03</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.41</v>
+        <v>2.77</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AD3" t="n">
         <v>8</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AF3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AK3" t="n">
         <v>1.4</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
@@ -1129,11 +1129,11 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>3</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
       <c r="AR3" t="n">
         <v>0</v>
       </c>
@@ -1144,70 +1144,70 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY3" t="n">
         <v>9</v>
       </c>
-      <c r="AX3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC3" t="n">
         <v>7</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BD3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BE3" t="n">
         <v>6</v>
       </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF3" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.73</v>
+        <v>2.42</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="BJ3" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="BK3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.82</v>
+        <v>3.59</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="BO3" t="n">
-        <v>4</v>
+        <v>5.44</v>
       </c>
       <c r="BP3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="4">
@@ -1215,7 +1215,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>7954030</v>
+        <v>8237911</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1235,35 +1235,35 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>['54']</t>
+          <t>['28', '51', '69', '77']</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1272,73 +1272,73 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S4" t="n">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="T4" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="U4" t="n">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="V4" t="n">
-        <v>2.85</v>
+        <v>2.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.73</v>
+        <v>1.49</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.27</v>
+        <v>5.63</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AD4" t="n">
         <v>10</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.8</v>
+        <v>2.21</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.55</v>
+        <v>1.11</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.39</v>
+        <v>2.5</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
@@ -1362,70 +1362,70 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV4" t="n">
         <v>2</v>
       </c>
       <c r="AW4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AX4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AY4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA4" t="n">
         <v>7</v>
       </c>
       <c r="BB4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.23</v>
+        <v>1.38</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.82</v>
+        <v>8.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.06</v>
+        <v>3.78</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="BK4" t="n">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.99</v>
+        <v>3.98</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.32</v>
+        <v>6.18</v>
       </c>
       <c r="BP4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="5">
@@ -1433,7 +1433,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>7954033</v>
+        <v>8237912</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1453,35 +1453,35 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4</v>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>['28', '51', '69', '77']</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1490,73 +1490,73 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>2.4</v>
+        <v>3.11</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S5" t="n">
-        <v>3.9</v>
+        <v>3.46</v>
       </c>
       <c r="T5" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="U5" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="V5" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="W5" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="X5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.58</v>
+        <v>2.73</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.73</v>
+        <v>3.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>9.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AH5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>2</v>
       </c>
-      <c r="AI5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AK5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
@@ -1580,55 +1580,55 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV5" t="n">
         <v>2</v>
       </c>
       <c r="AW5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AX5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BA5" t="n">
         <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.4</v>
+        <v>2.23</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.449999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.62</v>
+        <v>2.05</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="BI5" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="BK5" t="n">
-        <v>2.76</v>
+        <v>3.58</v>
       </c>
       <c r="BL5" t="n">
         <v>1.45</v>
@@ -1637,7 +1637,7 @@
         <v>3.98</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BO5" t="n">
         <v>6.18</v>
@@ -1651,7 +1651,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>7954029</v>
+        <v>8241468</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1708,73 +1708,73 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>6.05</v>
+        <v>5.75</v>
       </c>
       <c r="R6" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="S6" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="T6" t="n">
         <v>1.25</v>
       </c>
       <c r="U6" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="V6" t="n">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="X6" t="n">
-        <v>4.75</v>
+        <v>5.14</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AC6" t="n">
         <v>1.02</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>4.94</v>
+        <v>4.48</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AK6" t="n">
         <v>2.75</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
@@ -1825,43 +1825,43 @@
         <v>14</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.85</v>
+        <v>4.65</v>
       </c>
       <c r="BE6" t="n">
-        <v>10.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.54</v>
+        <v>2.88</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BJ6" t="n">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="BK6" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="BL6" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.23</v>
+        <v>2.48</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="BO6" t="n">
-        <v>2.96</v>
+        <v>3.91</v>
       </c>
       <c r="BP6" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="7">
@@ -1869,7 +1869,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>7954035</v>
+        <v>8237908</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1922,77 +1922,77 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>['18', '45+4']</t>
+          <t>['18', '45']</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="T7" t="n">
         <v>1.33</v>
       </c>
       <c r="U7" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="X7" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.5</v>
+        <v>5.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.69</v>
+        <v>1.22</v>
       </c>
       <c r="AC7" t="n">
         <v>1.02</v>
       </c>
       <c r="AD7" t="n">
-        <v>12.3</v>
+        <v>10</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.09</v>
+        <v>1.25</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -2016,16 +2016,16 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW7" t="n">
         <v>2</v>
       </c>
-      <c r="AV7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4</v>
-      </c>
       <c r="AX7" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AY7" t="n">
         <v>6</v>
@@ -2043,43 +2043,43 @@
         <v>8</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.85</v>
+        <v>10.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="BJ7" t="n">
         <v>2.01</v>
       </c>
       <c r="BK7" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="BM7" t="n">
-        <v>3.03</v>
+        <v>3.44</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.39</v>
+        <v>4.9</v>
       </c>
       <c r="BP7" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP7"/>
+  <dimension ref="A1:BP12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2080,6 +2080,1096 @@
       </c>
       <c r="BP7" t="n">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8238085</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>45899.59375</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ironi Kiryat Shmona</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Hapoel Petah Tikva</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8238083</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>45899.59375</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Maccabi Bnei Raina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Hapoel Tel Aviv</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>['37', '58']</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>['48', '90+4']</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8238082</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>45899.59375</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hapoel Haifa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Hapoel Katamon</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>['8', '45+1']</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8238084</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>45899.60416666666</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hapoel Be'er Sheva</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Ironi Tiberias</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>['2', '7', '18', '26', '53', '57', '83']</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="S11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8238086</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>45899.60416666666</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ashdod</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bnei Sakhnin</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>['3', '12']</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -2894,13 +2894,13 @@
         <v>1</v>
       </c>
       <c r="AW11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX11" t="n">
         <v>3</v>
       </c>
       <c r="AY11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AZ11" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP12"/>
+  <dimension ref="A1:BP13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3170,6 +3170,224 @@
       </c>
       <c r="BP12" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8237907</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>45900.58333333334</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Maccabi Tel Aviv</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Maccabi Netanya</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>['19', '21', '61', '71']</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP13"/>
+  <dimension ref="A1:BP14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3388,6 +3388,224 @@
       </c>
       <c r="BP13" t="n">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8238081</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>45900.60416666666</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Beitar Jerusalem</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Maccabi Haifa</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -3333,13 +3333,13 @@
         <v>9</v>
       </c>
       <c r="AX13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY13" t="n">
         <v>17</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA13" t="n">
         <v>5</v>
@@ -3551,13 +3551,13 @@
         <v>5</v>
       </c>
       <c r="AX14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY14" t="n">
         <v>8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA14" t="n">
         <v>1</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP14"/>
+  <dimension ref="A1:BP18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ8" t="n">
         <v>1</v>
@@ -3606,6 +3606,878 @@
       </c>
       <c r="BP14" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8237933</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>45913.57291666666</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hapoel Petah Tikva</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Maccabi Netanya</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>['22', '28', '72']</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8237926</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>45913.57291666666</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Bnei Sakhnin</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Hapoel Haifa</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>['63', '74']</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8237921</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>45913.58333333334</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ironi Kiryat Shmona</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Maccabi Bnei Raina</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>['28', '37', '72']</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V17" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X17" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8237929</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>45913.58333333334</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ironi Tiberias</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Maccabi Tel Aviv</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>['29', '45+1', '59', '59']</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X18" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP18"/>
+  <dimension ref="A1:BP19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3760,13 +3760,13 @@
         <v>0.58</v>
       </c>
       <c r="AU15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
         <v>6</v>
       </c>
       <c r="AW15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX15" t="n">
         <v>5</v>
@@ -4299,10 +4299,10 @@
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
         <v>1</v>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>['29', '45+1', '59', '59']</t>
+          <t>['29', '36', '45+1', '59']</t>
         </is>
       </c>
       <c r="Q18" t="n">
@@ -4417,7 +4417,7 @@
         <v>2</v>
       </c>
       <c r="AV18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW18" t="n">
         <v>2</v>
@@ -4429,7 +4429,7 @@
         <v>4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA18" t="n">
         <v>0</v>
@@ -4478,6 +4478,224 @@
       </c>
       <c r="BP18" t="n">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8237925</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>45914.59375</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hapoel Katamon</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Hapoel Be'er Sheva</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>['6', '28', '55', '90+3', '90+3']</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X19" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP19"/>
+  <dimension ref="A1:BP22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ15" t="n">
         <v>0</v>
@@ -3769,13 +3769,13 @@
         <v>12</v>
       </c>
       <c r="AX15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY15" t="n">
         <v>19</v>
       </c>
       <c r="AZ15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA15" t="n">
         <v>3</v>
@@ -4696,6 +4696,660 @@
       </c>
       <c r="BP19" t="n">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8237920</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>45915.58333333334</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Maccabi Haifa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Ashdod</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>6</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>['8', '39', '53', '85', '90+1']</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X20" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8237932</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>45915.60416666666</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hapoel Tel Aviv</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Beitar Jerusalem</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>['26', '90', '90+8']</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>['45+3', '78']</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X21" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8238080</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>45916.5625</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hapoel Petah Tikva</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Maccabi Tel Aviv</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>['19', '57', '83', '89']</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP22"/>
+  <dimension ref="A1:BP27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>3</v>
@@ -2222,7 +2222,7 @@
         <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ14" t="n">
         <v>1</v>
@@ -5350,6 +5350,1096 @@
       </c>
       <c r="BP22" t="n">
         <v>1.12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8237942</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>45920.57291666666</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Maccabi Bnei Raina</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Hapoel Petah Tikva</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>6</v>
+      </c>
+      <c r="N23" t="n">
+        <v>7</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>['31', '39', '42', '79', '85', '89']</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8237943</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>45920.57291666666</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ashdod</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Hapoel Tel Aviv</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>5</v>
+      </c>
+      <c r="N24" t="n">
+        <v>7</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>['1', '49']</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>['7', '13', '29', '42', '77']</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V24" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X24" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>8237935</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>45920.58333333334</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Beitar Jerusalem</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Ironi Kiryat Shmona</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>['32', '38']</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X25" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>8237944</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>45920.58333333334</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Maccabi Netanya</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Ironi Tiberias</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>5</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" t="n">
+        <v>7</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>['52', '75', '87', '90+4', '90+7']</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>['2', '54']</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V26" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X26" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8237946</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>45920.58333333334</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Maccabi Tel Aviv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Hapoel Katamon</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>['70', '90+4']</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X27" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -5743,10 +5743,10 @@
         <v>2</v>
       </c>
       <c r="BB24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD24" t="n">
         <v>2.84</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -6270,10 +6270,10 @@
         <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="Q27" t="n">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP27"/>
+  <dimension ref="A1:BP29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ10" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -6440,6 +6440,442 @@
       </c>
       <c r="BP27" t="n">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>8237941</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>45921.58333333334</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hapoel Be'er Sheva</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bnei Sakhnin</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>['3', '45+3']</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X28" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>8237930</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>45921.60416666666</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hapoel Haifa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Maccabi Haifa</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>['38']</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X29" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -6376,19 +6376,19 @@
         <v>3.16</v>
       </c>
       <c r="AU27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV27" t="n">
         <v>2</v>
       </c>
       <c r="AW27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX27" t="n">
         <v>6</v>
       </c>
       <c r="AY27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AZ27" t="n">
         <v>8</v>
@@ -6594,13 +6594,13 @@
         <v>4.92</v>
       </c>
       <c r="AU28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV28" t="n">
         <v>2</v>
       </c>
       <c r="AW28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX28" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP29"/>
+  <dimension ref="A1:BP26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1651,7 +1651,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>8241468</v>
+        <v>8237908</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1664,117 +1664,117 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>45893.59375</v>
+        <v>45894.58333333334</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>['9', '20']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>['33', '43', '45+3', '63']</t>
+          <t>['18', '45']</t>
         </is>
       </c>
       <c r="Q6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X6" t="n">
         <v>5.75</v>
       </c>
-      <c r="R6" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X6" t="n">
-        <v>5.14</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.65</v>
+        <v>5.63</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" t="n">
         <v>1.02</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF6" t="n">
-        <v>4.48</v>
+        <v>3.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.75</v>
+        <v>1.25</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
@@ -1783,11 +1783,11 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>1.5</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>3</v>
-      </c>
       <c r="AR6" t="n">
         <v>0</v>
       </c>
@@ -1798,70 +1798,70 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY6" t="n">
         <v>6</v>
       </c>
-      <c r="AV6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BC6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.65</v>
+        <v>3.82</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.699999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="BJ6" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="BK6" t="n">
-        <v>2.23</v>
+        <v>2.46</v>
       </c>
       <c r="BL6" t="n">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.48</v>
+        <v>3.44</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.91</v>
+        <v>4.9</v>
       </c>
       <c r="BP6" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="7">
@@ -1869,7 +1869,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>8237908</v>
+        <v>8238083</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1882,204 +1882,204 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>45894.58333333334</v>
+        <v>45899.59375</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>['37', '58']</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>['18', '45']</t>
+          <t>['48', '90+4']</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="U7" t="n">
         <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="W7" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="X7" t="n">
-        <v>5.75</v>
+        <v>6.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Z7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BE7" t="n">
         <v>8</v>
       </c>
-      <c r="AA7" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="BF7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BN7" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1.31</v>
       </c>
       <c r="BO7" t="n">
         <v>4.9</v>
       </c>
       <c r="BP7" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="8">
@@ -2087,7 +2087,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>8238085</v>
+        <v>8238082</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2107,89 +2107,89 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '45+1']</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AG8" t="n">
         <v>1.95</v>
@@ -2198,19 +2198,19 @@
         <v>1.85</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2234,70 +2234,70 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX8" t="n">
         <v>4</v>
       </c>
-      <c r="AV8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>7</v>
-      </c>
       <c r="AY8" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AZ8" t="n">
         <v>9</v>
       </c>
       <c r="BA8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC8" t="n">
         <v>8</v>
       </c>
-      <c r="BC8" t="n">
-        <v>11</v>
-      </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="9">
@@ -2305,7 +2305,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>8238083</v>
+        <v>8238085</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2325,197 +2325,197 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
         <v>4</v>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>['37', '58']</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>['48', '90+4']</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X9" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>5</v>
-      </c>
       <c r="AV9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AW9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY9" t="n">
         <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BB9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BC9" t="n">
         <v>11</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BK9" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2523,7 +2523,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>8238082</v>
+        <v>8238086</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2536,117 +2536,117 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>45899.59375</v>
+        <v>45899.60416666666</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>['8', '45+1']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>['3', '12']</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="S10" t="n">
-        <v>3.35</v>
+        <v>3.94</v>
       </c>
       <c r="T10" t="n">
         <v>1.4</v>
       </c>
       <c r="U10" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="V10" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="X10" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.34</v>
+        <v>1.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="AC10" t="n">
         <v>1.01</v>
       </c>
       <c r="AD10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.49</v>
+        <v>1.92</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2670,70 +2670,70 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC10" t="n">
         <v>9</v>
       </c>
-      <c r="AV10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>8</v>
-      </c>
       <c r="BD10" t="n">
-        <v>1.9</v>
+        <v>1.37</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.73</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.5</v>
+        <v>4.45</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.16</v>
+        <v>2.51</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="BK10" t="n">
-        <v>3.16</v>
+        <v>2.72</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="BM10" t="n">
-        <v>3.5</v>
+        <v>3.03</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.27</v>
+        <v>4.39</v>
       </c>
       <c r="BP10" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="11">
@@ -2959,7 +2959,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>8238086</v>
+        <v>8237907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2972,204 +2972,204 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>45899.60416666666</v>
+        <v>45900.58333333334</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['19', '21', '61', '71']</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>['3', '12']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="R12" t="n">
-        <v>2.05</v>
+        <v>2.59</v>
       </c>
       <c r="S12" t="n">
-        <v>3.94</v>
+        <v>6.25</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="U12" t="n">
-        <v>2.65</v>
+        <v>3.42</v>
       </c>
       <c r="V12" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="X12" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="AC12" t="n">
         <v>1.02</v>
       </c>
-      <c r="Z12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AD12" t="n">
-        <v>8.699999999999999</v>
+        <v>19</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AF12" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.09</v>
+        <v>1.47</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.7</v>
+        <v>2.41</v>
       </c>
       <c r="AI12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BK12" t="n">
         <v>1.9</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="BL12" t="n">
         <v>1.82</v>
       </c>
-      <c r="AK12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BM12" t="n">
-        <v>3.03</v>
+        <v>2.44</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.39</v>
+        <v>3.27</v>
       </c>
       <c r="BP12" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="13">
@@ -3177,7 +3177,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>8237907</v>
+        <v>8238081</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3190,42 +3190,42 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>45900.58333333334</v>
+        <v>45900.60416666666</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>['19', '21', '61', '71']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -3234,73 +3234,73 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>2.88</v>
       </c>
       <c r="R13" t="n">
-        <v>2.59</v>
+        <v>2.24</v>
       </c>
       <c r="S13" t="n">
-        <v>6.25</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="U13" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="V13" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="W13" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="X13" t="n">
-        <v>4.6</v>
+        <v>5.25</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.37</v>
+        <v>2.41</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.5</v>
+        <v>3.58</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.67</v>
+        <v>2.5</v>
       </c>
       <c r="AC13" t="n">
         <v>1.02</v>
       </c>
       <c r="AD13" t="n">
-        <v>19</v>
+        <v>14.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF13" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.93</v>
+        <v>2.52</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>3.05</v>
+        <v>1.44</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3324,70 +3324,70 @@
         <v>0</v>
       </c>
       <c r="AU13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY13" t="n">
         <v>8</v>
       </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
+      <c r="AZ13" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC13" t="n">
         <v>9</v>
       </c>
-      <c r="AX13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>8</v>
-      </c>
       <c r="BD13" t="n">
-        <v>1.15</v>
+        <v>1.76</v>
       </c>
       <c r="BE13" t="n">
-        <v>12</v>
+        <v>7.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.6</v>
+        <v>2.38</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.21</v>
+        <v>2.59</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="BJ13" t="n">
-        <v>2.31</v>
+        <v>1.96</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.9</v>
+        <v>2.17</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="BM13" t="n">
-        <v>2.44</v>
+        <v>2.99</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.27</v>
+        <v>4.32</v>
       </c>
       <c r="BP13" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="14">
@@ -3395,7 +3395,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>8238081</v>
+        <v>8237926</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -3408,19 +3408,19 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>45900.60416666666</v>
+        <v>45913.57291666666</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -3436,10 +3436,10 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -3448,164 +3448,164 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63', '74']</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="R14" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL14" t="n">
         <v>1.28</v>
       </c>
-      <c r="U14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="W14" t="n">
+      <c r="AM14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BG14" t="n">
         <v>1.53</v>
       </c>
-      <c r="X14" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Y14" t="n">
+      <c r="BH14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="BP14" t="n">
         <v>1.09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>1.13</v>
       </c>
     </row>
     <row r="15">
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AQ15" t="n">
         <v>0</v>
@@ -3831,7 +3831,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>8237926</v>
+        <v>8237929</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -3844,204 +3844,204 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>45913.57291666666</v>
+        <v>45913.58333333334</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>['63', '74']</t>
+          <t>['29', '36', '45+1', '59']</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>1.61</v>
       </c>
       <c r="T16" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="U16" t="n">
-        <v>2.65</v>
+        <v>3.14</v>
       </c>
       <c r="V16" t="n">
-        <v>2.87</v>
+        <v>2.25</v>
       </c>
       <c r="W16" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="X16" t="n">
-        <v>8.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC16" t="n">
         <v>1.02</v>
       </c>
-      <c r="Z16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AD16" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.04</v>
+        <v>4.68</v>
       </c>
       <c r="AG16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR16" t="n">
         <v>2.11</v>
       </c>
-      <c r="AH16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0.95</v>
-      </c>
       <c r="AS16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AU16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX16" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AY16" t="n">
         <v>4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="BA16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC16" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.38</v>
+        <v>8.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.05</v>
+        <v>13.75</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.98</v>
+        <v>1.09</v>
       </c>
       <c r="BG16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BN16" t="n">
         <v>1.53</v>
       </c>
-      <c r="BH16" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1.23</v>
-      </c>
       <c r="BO16" t="n">
-        <v>5.04</v>
+        <v>3.14</v>
       </c>
       <c r="BP16" t="n">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="17">
@@ -4267,7 +4267,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>8237929</v>
+        <v>8237925</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -4280,204 +4280,204 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>45913.58333333334</v>
+        <v>45914.59375</v>
       </c>
       <c r="F18" t="n">
         <v>3</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>['29', '36', '45+1', '59']</t>
+          <t>['6', '28', '55', '90+3', '90+3']</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>9.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="R18" t="n">
         <v>2.62</v>
       </c>
       <c r="S18" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="T18" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="U18" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="V18" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="W18" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Y18" t="n">
         <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.18</v>
+        <v>9.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AD18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE18" t="n">
         <v>1.18</v>
       </c>
       <c r="AF18" t="n">
-        <v>4.68</v>
+        <v>4.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AH18" t="n">
         <v>2.25</v>
       </c>
       <c r="AI18" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AM18" t="n">
         <v>1.03</v>
       </c>
       <c r="AN18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
         <v>3</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.11</v>
+        <v>1.54</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.11</v>
+        <v>1.54</v>
       </c>
       <c r="AU18" t="n">
         <v>2</v>
       </c>
       <c r="AV18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY18" t="n">
         <v>6</v>
       </c>
-      <c r="AY18" t="n">
-        <v>4</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>13.75</v>
+        <v>11</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="BJ18" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="BK18" t="n">
-        <v>2.09</v>
+        <v>2.36</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="BM18" t="n">
-        <v>2.31</v>
+        <v>2.71</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.14</v>
+        <v>3.72</v>
       </c>
       <c r="BP18" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="19">
@@ -4485,7 +4485,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>8237925</v>
+        <v>8237920</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -4498,204 +4498,204 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>45914.59375</v>
+        <v>45915.58333333334</v>
       </c>
       <c r="F19" t="n">
         <v>3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" t="n">
         <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>5</v>
       </c>
       <c r="N19" t="n">
         <v>6</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['8', '39', '53', '85', '90+1']</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>['6', '28', '55', '90+3', '90+3']</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>7.5</v>
+        <v>1.93</v>
       </c>
       <c r="R19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X19" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BH19" t="n">
         <v>2.62</v>
       </c>
-      <c r="S19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V19" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X19" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AL19" t="n">
+      <c r="BI19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BP19" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>1.2</v>
       </c>
     </row>
     <row r="20">
@@ -4703,7 +4703,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>8237920</v>
+        <v>8237932</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -4716,117 +4716,117 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>45915.58333333334</v>
+        <v>45915.60416666666</v>
       </c>
       <c r="F20" t="n">
         <v>3</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>['26', '90', '90+8']</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>['45+3', '78']</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X20" t="n">
         <v>6</v>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>['8', '39', '53', '85', '90+1']</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>['31']</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="V20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="X20" t="n">
-        <v>5.35</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.35</v>
+        <v>2.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AF20" t="n">
-        <v>4</v>
+        <v>3.52</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AM20" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="AN20" t="n">
         <v>3</v>
@@ -4841,79 +4841,79 @@
         <v>1.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.77</v>
+        <v>1.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.78</v>
+        <v>3.05</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.55</v>
+        <v>4.25</v>
       </c>
       <c r="AU20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>10</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>11</v>
       </c>
       <c r="BA20" t="n">
         <v>5</v>
       </c>
       <c r="BB20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BC20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.800000000000001</v>
+        <v>6.05</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.9</v>
+        <v>1.89</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="BH20" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="BK20" t="n">
-        <v>2.65</v>
+        <v>2.96</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.77</v>
+        <v>1.49</v>
       </c>
       <c r="BM20" t="n">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.25</v>
+        <v>4.86</v>
       </c>
       <c r="BP20" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="21">
@@ -4921,7 +4921,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>8237932</v>
+        <v>8237943</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -4934,204 +4934,204 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>45915.60416666666</v>
+        <v>45920.57291666666</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>Ashdod</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>Hapoel Tel Aviv</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
+        <v>7</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>['1', '49']</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>['7', '13', '29', '42', '77']</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X21" t="n">
         <v>5</v>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>['26', '90', '90+8']</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>['45+3', '78']</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X21" t="n">
-        <v>6</v>
-      </c>
       <c r="Y21" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.26</v>
+        <v>3.98</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
         <v>1.01</v>
       </c>
       <c r="AD21" t="n">
-        <v>9.300000000000001</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.52</v>
+        <v>4.25</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AL21" t="n">
         <v>1.25</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AN21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.2</v>
+        <v>1.87</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.05</v>
+        <v>1.67</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.25</v>
+        <v>3.54</v>
       </c>
       <c r="AU21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AW21" t="n">
         <v>5</v>
       </c>
       <c r="AX21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ21" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BB21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC21" t="n">
         <v>6</v>
       </c>
-      <c r="BC21" t="n">
-        <v>11</v>
-      </c>
       <c r="BD21" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="BE21" t="n">
-        <v>6.05</v>
+        <v>6.93</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="BH21" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="BK21" t="n">
-        <v>2.96</v>
+        <v>2.44</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="BM21" t="n">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.86</v>
+        <v>5.05</v>
       </c>
       <c r="BP21" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="22">
@@ -5139,7 +5139,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>8238080</v>
+        <v>8237942</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -5152,204 +5152,204 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>45916.5625</v>
+        <v>45920.57291666666</v>
       </c>
       <c r="F22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Maccabi Bnei Raina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Hapoel Petah Tikva</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Hapoel Petah Tikva</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Maccabi Tel Aviv</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
+      <c r="M22" t="n">
+        <v>6</v>
+      </c>
+      <c r="N22" t="n">
+        <v>7</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>['31', '39', '42', '79', '85', '89']</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
+      <c r="AO22" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="AP22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU22" t="n">
         <v>4</v>
       </c>
-      <c r="N22" t="n">
-        <v>4</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>['19', '57', '83', '89']</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X22" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z22" t="n">
+      <c r="AV22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB22" t="n">
         <v>7</v>
       </c>
-      <c r="AA22" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY22" t="n">
+      <c r="BC22" t="n">
         <v>8</v>
       </c>
-      <c r="AZ22" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>7</v>
-      </c>
       <c r="BD22" t="n">
-        <v>8.800000000000001</v>
+        <v>2.14</v>
       </c>
       <c r="BE22" t="n">
-        <v>11.7</v>
+        <v>5.85</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.13</v>
+        <v>2.14</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="BH22" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="BK22" t="n">
-        <v>2.2</v>
+        <v>2.71</v>
       </c>
       <c r="BL22" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="BM22" t="n">
-        <v>3.06</v>
+        <v>3.8</v>
       </c>
       <c r="BN22" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.46</v>
+        <v>5.27</v>
       </c>
       <c r="BP22" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="23">
@@ -5357,7 +5357,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>8237942</v>
+        <v>8237944</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -5370,204 +5370,204 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>45920.57291666666</v>
+        <v>45920.58333333334</v>
       </c>
       <c r="F23" t="n">
         <v>4</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N23" t="n">
         <v>7</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>['71']</t>
+          <t>['52', '75', '87', '90+4', '90+7']</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>['31', '39', '42', '79', '85', '89']</t>
+          <t>['2', '54']</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>3.28</v>
+        <v>2.25</v>
       </c>
       <c r="R23" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S23" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="T23" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="U23" t="n">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="V23" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="W23" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="X23" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.81</v>
+        <v>1.64</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.38</v>
+        <v>3.55</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.23</v>
+        <v>4.4</v>
       </c>
       <c r="AC23" t="n">
         <v>1.01</v>
       </c>
       <c r="AD23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AF23" t="n">
-        <v>3.35</v>
+        <v>3.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.31</v>
+        <v>2.21</v>
       </c>
       <c r="AN23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="AQ23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.2</v>
+        <v>0.51</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.56</v>
+        <v>0.51</v>
       </c>
       <c r="AU23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX23" t="n">
         <v>4</v>
       </c>
-      <c r="AV23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW23" t="n">
+      <c r="AY23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>10</v>
       </c>
-      <c r="AX23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>23</v>
-      </c>
       <c r="BA23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="BB23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BC23" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BD23" t="n">
-        <v>2.14</v>
+        <v>1.56</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF23" t="n">
-        <v>2.14</v>
+        <v>2.92</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="BH23" t="n">
-        <v>2.3</v>
+        <v>2.71</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="BJ23" t="n">
-        <v>1.77</v>
+        <v>2.03</v>
       </c>
       <c r="BK23" t="n">
-        <v>2.71</v>
+        <v>2.15</v>
       </c>
       <c r="BL23" t="n">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="BM23" t="n">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="BN23" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="BO23" t="n">
-        <v>5.27</v>
+        <v>4.06</v>
       </c>
       <c r="BP23" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="24">
@@ -5575,7 +5575,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>8237943</v>
+        <v>8237935</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -5588,96 +5588,96 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>45920.57291666666</v>
+        <v>45920.58333333334</v>
       </c>
       <c r="F24" t="n">
         <v>4</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="J24" t="n">
-        <v>4</v>
-      </c>
-      <c r="K24" t="n">
-        <v>5</v>
-      </c>
-      <c r="L24" t="n">
-        <v>2</v>
-      </c>
-      <c r="M24" t="n">
-        <v>5</v>
-      </c>
       <c r="N24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>['1', '49']</t>
+          <t>['32', '38']</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>['7', '13', '29', '42', '77']</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>4.2</v>
+        <v>1.94</v>
       </c>
       <c r="R24" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="S24" t="n">
-        <v>2.29</v>
+        <v>6.28</v>
       </c>
       <c r="T24" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="U24" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="V24" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.5</v>
+        <v>1.46</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>5.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AD24" t="n">
-        <v>15</v>
+        <v>13.9</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF24" t="n">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="AG24" t="n">
         <v>1.68</v>
@@ -5686,40 +5686,40 @@
         <v>2.05</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.18</v>
+        <v>1.81</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.22</v>
+        <v>2.49</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.87</v>
+        <v>0.8</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.67</v>
+        <v>0.84</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.54</v>
+        <v>1.64</v>
       </c>
       <c r="AU24" t="n">
         <v>3</v>
@@ -5728,64 +5728,64 @@
         <v>8</v>
       </c>
       <c r="AW24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB24" t="n">
         <v>6</v>
       </c>
-      <c r="AY24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>4</v>
-      </c>
       <c r="BC24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.84</v>
+        <v>1.29</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.93</v>
+        <v>9.25</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.73</v>
+        <v>5.27</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="BH24" t="n">
-        <v>2.35</v>
+        <v>3.09</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1.91</v>
+        <v>2.24</v>
       </c>
       <c r="BK24" t="n">
-        <v>2.44</v>
+        <v>2.23</v>
       </c>
       <c r="BL24" t="n">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="BM24" t="n">
-        <v>3.38</v>
+        <v>2.49</v>
       </c>
       <c r="BN24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="BP24" t="n">
         <v>1.23</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>1.09</v>
       </c>
     </row>
     <row r="25">
@@ -5793,7 +5793,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>8237935</v>
+        <v>8237941</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -5806,29 +5806,29 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>45920.58333333334</v>
+        <v>45921.58333333334</v>
       </c>
       <c r="F25" t="n">
         <v>4</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="I25" t="n">
         <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L25" t="n">
         <v>2</v>
@@ -5841,169 +5841,169 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>['32', '38']</t>
+          <t>['3', '45+3']</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="Q25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="U25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V25" t="n">
         <v>1.94</v>
       </c>
-      <c r="R25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S25" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="U25" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="V25" t="n">
-        <v>2.5</v>
-      </c>
       <c r="W25" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="X25" t="n">
-        <v>5.75</v>
+        <v>4.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.46</v>
+        <v>1.13</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.1</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="AB25" t="n">
-        <v>5.2</v>
+        <v>18.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AD25" t="n">
-        <v>13.9</v>
+        <v>23</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AF25" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.68</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.05</v>
+        <v>3.13</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AM25" t="n">
-        <v>2.49</v>
+        <v>6.52</v>
       </c>
       <c r="AN25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.8</v>
+        <v>3.91</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.84</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.64</v>
+        <v>4.92</v>
       </c>
       <c r="AU25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AV25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA25" t="n">
         <v>8</v>
       </c>
-      <c r="AW25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1</v>
-      </c>
       <c r="BB25" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BC25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="BE25" t="n">
-        <v>9.25</v>
+        <v>18.75</v>
       </c>
       <c r="BF25" t="n">
-        <v>5.27</v>
+        <v>11</v>
       </c>
       <c r="BG25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="BP25" t="n">
         <v>1.28</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>1.23</v>
       </c>
     </row>
     <row r="26">
@@ -6011,7 +6011,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>8237944</v>
+        <v>8237930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -6024,857 +6024,203 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>45920.58333333334</v>
+        <v>45921.60416666666</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
       </c>
       <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="L26" t="n">
-        <v>5</v>
-      </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>['52', '75', '87', '90+4', '90+7']</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>['2', '54']</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="Q26" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V26" t="n">
         <v>2.25</v>
       </c>
-      <c r="R26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S26" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U26" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V26" t="n">
-        <v>2.73</v>
-      </c>
       <c r="W26" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="X26" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="Y26" t="n">
         <v>1.09</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.64</v>
+        <v>3.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>4.4</v>
+        <v>1.62</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AD26" t="n">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>3.73</v>
+        <v>4.33</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.87</v>
+        <v>2.26</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.95</v>
+        <v>2.22</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AM26" t="n">
-        <v>2.21</v>
+        <v>1.15</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.17</v>
+        <v>2.27</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.51</v>
+        <v>1.51</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.68</v>
+        <v>3.78</v>
       </c>
       <c r="AU26" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AV26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AW26" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AX26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY26" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
         <v>10</v>
       </c>
       <c r="BA26" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BB26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BC26" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.56</v>
+        <v>3.1</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="BF26" t="n">
-        <v>2.92</v>
+        <v>1.51</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BH26" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="BJ26" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="BK26" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="BL26" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="BM26" t="n">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="BN26" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="BO26" t="n">
-        <v>4.06</v>
+        <v>4.26</v>
       </c>
       <c r="BP26" t="n">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="n">
-        <v>8237946</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Israel Israeli Premier League</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>45920.58333333334</v>
-      </c>
-      <c r="F27" t="n">
-        <v>4</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Maccabi Tel Aviv</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Hapoel Katamon</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>['70', '90+4']</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>['67']</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3</v>
-      </c>
-      <c r="S27" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="U27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="X27" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="BI27" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BJ27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BK27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BM27" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="BN27" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BO27" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="BP27" t="n">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="n">
-        <v>8237941</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Israel Israeli Premier League</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>45921.58333333334</v>
-      </c>
-      <c r="F28" t="n">
-        <v>4</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Hapoel Be'er Sheva</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Bnei Sakhnin</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3</v>
-      </c>
-      <c r="L28" t="n">
-        <v>2</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>['3', '45+3']</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>['19']</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R28" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="U28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="X28" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>9.029999999999999</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>18.06</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>26</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BO28" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="n">
-        <v>8237930</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Israel Israeli Premier League</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>45921.60416666666</v>
-      </c>
-      <c r="F29" t="n">
-        <v>4</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Hapoel Haifa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Maccabi Haifa</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>['38']</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>['14']</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="U29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X29" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BH29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BI29" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BJ29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BK29" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="BL29" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BM29" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="BN29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BO29" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="BP29" t="n">
         <v>1.14</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP26"/>
+  <dimension ref="A1:BP29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1651,7 +1651,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>8237908</v>
+        <v>8291602</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1664,204 +1664,204 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>45894.58333333334</v>
+        <v>45893.59375</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>['9', '20']</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>['18', '45']</t>
+          <t>['33', '42', '45+3', '63']</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX6" t="n">
         <v>10</v>
       </c>
-      <c r="AE6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA6" t="n">
         <v>4</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="BB6" t="n">
         <v>10</v>
       </c>
-      <c r="AW6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>8</v>
-      </c>
       <c r="BC6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BK6" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1869,7 +1869,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>8238083</v>
+        <v>8237908</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1882,204 +1882,204 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>45899.59375</v>
+        <v>45894.58333333334</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>['18', '45']</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X7" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
         <v>4</v>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>['37', '58']</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>['48', '90+4']</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W7" t="n">
+      <c r="AV7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="BF7" t="n">
         <v>1.37</v>
       </c>
-      <c r="X7" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.55</v>
-      </c>
       <c r="BG7" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1.77</v>
+        <v>2.01</v>
       </c>
       <c r="BK7" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="BM7" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="BO7" t="n">
         <v>4.9</v>
       </c>
       <c r="BP7" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="8">
@@ -2087,7 +2087,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>8238082</v>
+        <v>8238085</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2107,89 +2107,89 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>['8', '45+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>1.95</v>
@@ -2198,19 +2198,19 @@
         <v>1.85</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2234,70 +2234,70 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AV8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY8" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AZ8" t="n">
         <v>9</v>
       </c>
       <c r="BA8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BB8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.73</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BK8" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BO8" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="BP8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2305,7 +2305,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>8238085</v>
+        <v>8238082</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2325,89 +2325,89 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '45+1']</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AG9" t="n">
         <v>1.95</v>
@@ -2416,19 +2416,19 @@
         <v>1.85</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2452,70 +2452,70 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX9" t="n">
         <v>4</v>
       </c>
-      <c r="AV9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>7</v>
-      </c>
       <c r="AY9" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AZ9" t="n">
         <v>9</v>
       </c>
       <c r="BA9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC9" t="n">
         <v>8</v>
       </c>
-      <c r="BC9" t="n">
-        <v>11</v>
-      </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="10">
@@ -2523,7 +2523,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>8238086</v>
+        <v>8238083</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2536,204 +2536,204 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>45899.60416666666</v>
+        <v>45899.59375</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['37', '58']</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>['3', '12']</t>
+          <t>['48', '90+4']</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="R10" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="S10" t="n">
-        <v>3.94</v>
+        <v>2.2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="U10" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="X10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.85</v>
+        <v>4.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>4</v>
+        <v>1.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AK10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BN10" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BO10" t="n">
-        <v>4.39</v>
+        <v>4.9</v>
       </c>
       <c r="BP10" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="11">
@@ -2959,7 +2959,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>8237907</v>
+        <v>8238086</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2972,204 +2972,204 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>45900.58333333334</v>
+        <v>45899.60416666666</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>['3', '12']</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB12" t="n">
         <v>4</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
+      <c r="AC12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
         <v>4</v>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>['19', '21', '61', '71']</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="S12" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="V12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z12" t="n">
+      <c r="AV12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD12" t="n">
         <v>1.37</v>
       </c>
-      <c r="AA12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>1.15</v>
-      </c>
       <c r="BE12" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.6</v>
+        <v>4.45</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.21</v>
+        <v>2.51</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="BJ12" t="n">
-        <v>2.31</v>
+        <v>1.94</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.9</v>
+        <v>2.72</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="BM12" t="n">
-        <v>2.44</v>
+        <v>3.03</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.27</v>
+        <v>4.39</v>
       </c>
       <c r="BP12" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="13">
@@ -3177,7 +3177,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>8238081</v>
+        <v>8237907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3190,117 +3190,117 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>45900.60416666666</v>
+        <v>45900.58333333334</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
+          <t>['19', '21', '61', '71']</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="Q13" t="n">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>2.24</v>
+        <v>2.59</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>6.25</v>
       </c>
       <c r="T13" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="V13" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="X13" t="n">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.41</v>
+        <v>1.37</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.58</v>
+        <v>5.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.5</v>
+        <v>7.67</v>
       </c>
       <c r="AC13" t="n">
         <v>1.02</v>
       </c>
       <c r="AD13" t="n">
-        <v>14.3</v>
+        <v>19</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF13" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.52</v>
+        <v>1.93</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.44</v>
+        <v>3.05</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3324,70 +3324,70 @@
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AV13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA13" t="n">
         <v>5</v>
       </c>
-      <c r="AX13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY13" t="n">
+      <c r="BB13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC13" t="n">
         <v>8</v>
       </c>
-      <c r="AZ13" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>9</v>
-      </c>
       <c r="BD13" t="n">
-        <v>1.76</v>
+        <v>1.15</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.01</v>
+        <v>12</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.38</v>
+        <v>6.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.59</v>
+        <v>3.21</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.96</v>
+        <v>2.31</v>
       </c>
       <c r="BK13" t="n">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="BM13" t="n">
-        <v>2.99</v>
+        <v>2.44</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.32</v>
+        <v>3.27</v>
       </c>
       <c r="BP13" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="14">
@@ -3395,7 +3395,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>8237926</v>
+        <v>8238081</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -3408,19 +3408,19 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>45913.57291666666</v>
+        <v>45900.60416666666</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -3436,10 +3436,10 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -3448,77 +3448,77 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>['63', '74']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="U14" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="V14" t="n">
-        <v>2.87</v>
+        <v>2.34</v>
       </c>
       <c r="W14" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="X14" t="n">
-        <v>8.199999999999999</v>
+        <v>5.25</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC14" t="n">
         <v>1.02</v>
       </c>
-      <c r="Z14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AD14" t="n">
-        <v>8.800000000000001</v>
+        <v>14.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AF14" t="n">
-        <v>3.04</v>
+        <v>4.33</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.11</v>
+        <v>1.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.7</v>
+        <v>2.29</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.9</v>
+        <v>2.52</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -3527,85 +3527,85 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA14" t="n">
         <v>1</v>
       </c>
-      <c r="AV14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>7</v>
-      </c>
       <c r="BB14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BC14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BD14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="BF14" t="n">
         <v>2.38</v>
       </c>
-      <c r="BE14" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.98</v>
-      </c>
       <c r="BG14" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.32</v>
+        <v>2.59</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="BK14" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="BM14" t="n">
-        <v>3.42</v>
+        <v>2.99</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.04</v>
+        <v>4.32</v>
       </c>
       <c r="BP14" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="15">
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ15" t="n">
         <v>0</v>
@@ -3831,7 +3831,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>8237929</v>
+        <v>8237926</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -3844,204 +3844,204 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>45913.58333333334</v>
+        <v>45913.57291666666</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>['63', '74']</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AU16" t="n">
         <v>1</v>
       </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>4</v>
-      </c>
-      <c r="N16" t="n">
-        <v>5</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>['9']</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>['29', '36', '45+1', '59']</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X16" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2</v>
-      </c>
       <c r="AV16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX16" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AY16" t="n">
         <v>4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC16" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="BD16" t="n">
-        <v>8.9</v>
+        <v>2.38</v>
       </c>
       <c r="BE16" t="n">
-        <v>13.75</v>
+        <v>6.05</v>
       </c>
       <c r="BF16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="BP16" t="n">
         <v>1.09</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>1.27</v>
       </c>
     </row>
     <row r="17">
@@ -4267,7 +4267,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>8237925</v>
+        <v>8237929</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -4280,204 +4280,204 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>45914.59375</v>
+        <v>45913.58333333334</v>
       </c>
       <c r="F18" t="n">
         <v>3</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
         <v>1</v>
       </c>
       <c r="M18" t="n">
+        <v>4</v>
+      </c>
+      <c r="N18" t="n">
         <v>5</v>
       </c>
-      <c r="N18" t="n">
-        <v>6</v>
-      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>['6', '28', '55', '90+3', '90+3']</t>
+          <t>['29', '36', '45+1', '59']</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R18" t="n">
         <v>2.62</v>
       </c>
       <c r="S18" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="T18" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="U18" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="V18" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="X18" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Y18" t="n">
         <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>9.6</v>
+        <v>7.18</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE18" t="n">
         <v>1.18</v>
       </c>
       <c r="AF18" t="n">
-        <v>4.5</v>
+        <v>4.68</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AH18" t="n">
         <v>2.25</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AM18" t="n">
         <v>1.03</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>3</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.54</v>
+        <v>2.11</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.54</v>
+        <v>2.11</v>
       </c>
       <c r="AU18" t="n">
         <v>2</v>
       </c>
       <c r="AV18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY18" t="n">
         <v>4</v>
       </c>
-      <c r="AX18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>6</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.8</v>
+        <v>8.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>11</v>
+        <v>13.75</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BH18" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="BJ18" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="BK18" t="n">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="BM18" t="n">
-        <v>2.71</v>
+        <v>2.31</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.72</v>
+        <v>3.14</v>
       </c>
       <c r="BP18" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="19">
@@ -4485,7 +4485,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>8237920</v>
+        <v>8237925</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -4498,204 +4498,204 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>45915.58333333334</v>
+        <v>45914.59375</v>
       </c>
       <c r="F19" t="n">
         <v>3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
       </c>
       <c r="N19" t="n">
         <v>6</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>['8', '39', '53', '85', '90+1']</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>['6', '28', '55', '90+3', '90+3']</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>1.93</v>
+        <v>7.5</v>
       </c>
       <c r="R19" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="S19" t="n">
-        <v>5.3</v>
+        <v>1.68</v>
       </c>
       <c r="T19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X19" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BG19" t="n">
         <v>1.32</v>
       </c>
-      <c r="U19" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="V19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="X19" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK19" t="n">
+      <c r="BH19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="BP19" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>1.14</v>
       </c>
     </row>
     <row r="20">
@@ -4703,7 +4703,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>8237932</v>
+        <v>8237920</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -4716,117 +4716,117 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>45915.60416666666</v>
+        <v>45915.58333333334</v>
       </c>
       <c r="F20" t="n">
         <v>3</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>['26', '90', '90+8']</t>
+          <t>['8', '39', '53', '85', '90+1']</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>['45+3', '78']</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>3.52</v>
+        <v>1.93</v>
       </c>
       <c r="R20" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="S20" t="n">
-        <v>3.01</v>
+        <v>5.3</v>
       </c>
       <c r="T20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X20" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.35</v>
       </c>
-      <c r="U20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X20" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AA20" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>5.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AD20" t="n">
-        <v>9.300000000000001</v>
+        <v>18</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.52</v>
+        <v>4</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="AN20" t="n">
         <v>3</v>
@@ -4841,79 +4841,79 @@
         <v>1.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.2</v>
+        <v>1.77</v>
       </c>
       <c r="AS20" t="n">
-        <v>3.05</v>
+        <v>1.78</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.25</v>
+        <v>3.55</v>
       </c>
       <c r="AU20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AV20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY20" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AZ20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA20" t="n">
         <v>5</v>
       </c>
       <c r="BB20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BC20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.05</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.89</v>
+        <v>3.9</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="BK20" t="n">
-        <v>2.96</v>
+        <v>2.65</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="BM20" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.86</v>
+        <v>4.25</v>
       </c>
       <c r="BP20" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="21">
@@ -4921,7 +4921,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>8237943</v>
+        <v>8237932</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -4934,204 +4934,204 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>45920.57291666666</v>
+        <v>45915.60416666666</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" t="n">
         <v>5</v>
       </c>
-      <c r="L21" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>7</v>
-      </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>['1', '49']</t>
+          <t>['26', '90', '90+8']</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>['7', '13', '29', '42', '77']</t>
+          <t>['45+3', '78']</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="R21" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="S21" t="n">
-        <v>2.29</v>
+        <v>3.01</v>
       </c>
       <c r="T21" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="U21" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="V21" t="n">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="W21" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="X21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.98</v>
+        <v>3.26</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="AC21" t="n">
         <v>1.01</v>
       </c>
       <c r="AD21" t="n">
-        <v>15</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AF21" t="n">
-        <v>4.25</v>
+        <v>3.52</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AL21" t="n">
         <v>1.25</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.87</v>
+        <v>1.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.67</v>
+        <v>3.05</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.54</v>
+        <v>4.25</v>
       </c>
       <c r="AU21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AW21" t="n">
         <v>5</v>
       </c>
       <c r="AX21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB21" t="n">
         <v>6</v>
       </c>
-      <c r="AY21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>4</v>
-      </c>
       <c r="BC21" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>6.93</v>
+        <v>6.05</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="BH21" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="BK21" t="n">
-        <v>2.44</v>
+        <v>2.96</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="BM21" t="n">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BO21" t="n">
-        <v>5.05</v>
+        <v>4.86</v>
       </c>
       <c r="BP21" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="22">
@@ -5139,7 +5139,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>8237942</v>
+        <v>8291605</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -5152,204 +5152,204 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>45920.57291666666</v>
+        <v>45916.5625</v>
       </c>
       <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hapoel Petah Tikva</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Maccabi Tel Aviv</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>4</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Maccabi Bnei Raina</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Hapoel Petah Tikva</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>6</v>
-      </c>
       <c r="N22" t="n">
+        <v>4</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>['19', '57', '83', '89']</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV22" t="n">
         <v>7</v>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>['71']</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>['31', '39', '42', '79', '85', '89']</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="V22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AU22" t="n">
+      <c r="AW22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA22" t="n">
         <v>4</v>
       </c>
-      <c r="AV22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1</v>
-      </c>
       <c r="BB22" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC22" t="n">
         <v>7</v>
       </c>
-      <c r="BC22" t="n">
-        <v>8</v>
-      </c>
       <c r="BD22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BK22" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="BL22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BM22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BN22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BO22" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="BP22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -5357,7 +5357,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>8237944</v>
+        <v>8237942</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -5370,204 +5370,204 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>45920.58333333334</v>
+        <v>45920.57291666666</v>
       </c>
       <c r="F23" t="n">
         <v>4</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>5</v>
-      </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N23" t="n">
         <v>7</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>['52', '75', '87', '90+4', '90+7']</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>['2', '54']</t>
+          <t>['31', '39', '42', '79', '85', '89']</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>2.25</v>
+        <v>3.28</v>
       </c>
       <c r="R23" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S23" t="n">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="T23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W23" t="n">
         <v>1.36</v>
       </c>
-      <c r="U23" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V23" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.44</v>
-      </c>
       <c r="X23" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.64</v>
+        <v>2.81</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.55</v>
+        <v>3.38</v>
       </c>
       <c r="AB23" t="n">
-        <v>4.4</v>
+        <v>2.23</v>
       </c>
       <c r="AC23" t="n">
         <v>1.01</v>
       </c>
       <c r="AD23" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AF23" t="n">
-        <v>3.73</v>
+        <v>3.35</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AJ23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BI23" t="n">
         <v>1.95</v>
       </c>
-      <c r="AK23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BG23" t="n">
+      <c r="BJ23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BL23" t="n">
         <v>1.38</v>
       </c>
-      <c r="BH23" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1.59</v>
-      </c>
       <c r="BM23" t="n">
-        <v>2.85</v>
+        <v>3.8</v>
       </c>
       <c r="BN23" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.06</v>
+        <v>5.27</v>
       </c>
       <c r="BP23" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="24">
@@ -5575,7 +5575,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>8237935</v>
+        <v>8237943</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -5588,96 +5588,96 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>45920.58333333334</v>
+        <v>45920.57291666666</v>
       </c>
       <c r="F24" t="n">
         <v>4</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L24" t="n">
         <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>['32', '38']</t>
+          <t>['1', '49']</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['7', '13', '29', '42', '77']</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>1.94</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="S24" t="n">
-        <v>6.28</v>
+        <v>2.29</v>
       </c>
       <c r="T24" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="U24" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="V24" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="W24" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="X24" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.46</v>
+        <v>4.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="AB24" t="n">
-        <v>5.2</v>
+        <v>1.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AD24" t="n">
-        <v>13.9</v>
+        <v>15</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF24" t="n">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="AG24" t="n">
         <v>1.68</v>
@@ -5686,40 +5686,40 @@
         <v>2.05</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.81</v>
+        <v>2.18</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AM24" t="n">
-        <v>2.49</v>
+        <v>1.22</v>
       </c>
       <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
         <v>1</v>
       </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
       <c r="AP24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.8</v>
+        <v>1.87</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.84</v>
+        <v>1.67</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.64</v>
+        <v>3.54</v>
       </c>
       <c r="AU24" t="n">
         <v>3</v>
@@ -5728,64 +5728,64 @@
         <v>8</v>
       </c>
       <c r="AW24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB24" t="n">
         <v>4</v>
       </c>
-      <c r="AX24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB24" t="n">
+      <c r="BC24" t="n">
         <v>6</v>
       </c>
-      <c r="BC24" t="n">
-        <v>7</v>
-      </c>
       <c r="BD24" t="n">
-        <v>1.29</v>
+        <v>2.84</v>
       </c>
       <c r="BE24" t="n">
-        <v>9.25</v>
+        <v>6.93</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.27</v>
+        <v>1.73</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.09</v>
+        <v>2.35</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="BJ24" t="n">
-        <v>2.24</v>
+        <v>1.91</v>
       </c>
       <c r="BK24" t="n">
-        <v>2.23</v>
+        <v>2.44</v>
       </c>
       <c r="BL24" t="n">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="BM24" t="n">
-        <v>2.49</v>
+        <v>3.38</v>
       </c>
       <c r="BN24" t="n">
-        <v>1.45</v>
+        <v>1.23</v>
       </c>
       <c r="BO24" t="n">
-        <v>3.41</v>
+        <v>5.05</v>
       </c>
       <c r="BP24" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="25">
@@ -5793,7 +5793,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>8237941</v>
+        <v>8237944</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -5806,204 +5806,204 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>45921.58333333334</v>
+        <v>45920.58333333334</v>
       </c>
       <c r="F25" t="n">
         <v>4</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>['3', '45+3']</t>
+          <t>['52', '75', '87', '90+4', '90+7']</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>['2', '54']</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="R25" t="n">
-        <v>3.22</v>
+        <v>2.15</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>4.75</v>
       </c>
       <c r="T25" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="U25" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="V25" t="n">
-        <v>1.94</v>
+        <v>2.73</v>
       </c>
       <c r="W25" t="n">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="X25" t="n">
-        <v>4.15</v>
+        <v>6</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.13</v>
+        <v>1.64</v>
       </c>
       <c r="AA25" t="n">
-        <v>9.029999999999999</v>
+        <v>3.55</v>
       </c>
       <c r="AB25" t="n">
-        <v>18.06</v>
+        <v>4.4</v>
       </c>
       <c r="AC25" t="n">
         <v>1.01</v>
       </c>
       <c r="AD25" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY25" t="n">
         <v>23</v>
       </c>
-      <c r="AE25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AG25" t="n">
+      <c r="AZ25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BN25" t="n">
         <v>1.32</v>
       </c>
-      <c r="AH25" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>26</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>1.49</v>
-      </c>
       <c r="BO25" t="n">
-        <v>3.13</v>
+        <v>4.06</v>
       </c>
       <c r="BP25" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="26">
@@ -6011,7 +6011,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>8237930</v>
+        <v>8291603</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -6024,203 +6024,857 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>45921.60416666666</v>
+        <v>45920.58333333334</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
         <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>['70', '90+4']</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
         <v>3</v>
       </c>
       <c r="AO26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.78</v>
+        <v>3.16</v>
       </c>
       <c r="AU26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW26" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AX26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY26" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AZ26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BB26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BC26" t="n">
         <v>9</v>
       </c>
       <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8237935</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>45920.58333333334</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Beitar Jerusalem</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Ironi Kiryat Shmona</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>['32', '38']</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X27" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>8237941</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>45921.58333333334</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hapoel Be'er Sheva</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bnei Sakhnin</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>['3', '45+3']</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X28" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>8237930</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>45921.60416666666</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hapoel Haifa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Maccabi Haifa</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>['38']</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X29" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD29" t="n">
         <v>3.1</v>
       </c>
-      <c r="BE26" t="n">
+      <c r="BE29" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="BF26" t="n">
+      <c r="BF29" t="n">
         <v>1.51</v>
       </c>
-      <c r="BG26" t="n">
+      <c r="BG29" t="n">
         <v>1.41</v>
       </c>
-      <c r="BH26" t="n">
+      <c r="BH29" t="n">
         <v>2.6</v>
       </c>
-      <c r="BI26" t="n">
+      <c r="BI29" t="n">
         <v>1.76</v>
       </c>
-      <c r="BJ26" t="n">
+      <c r="BJ29" t="n">
         <v>1.95</v>
       </c>
-      <c r="BK26" t="n">
+      <c r="BK29" t="n">
         <v>2.21</v>
       </c>
-      <c r="BL26" t="n">
+      <c r="BL29" t="n">
         <v>1.58</v>
       </c>
-      <c r="BM26" t="n">
+      <c r="BM29" t="n">
         <v>3.04</v>
       </c>
-      <c r="BN26" t="n">
+      <c r="BN29" t="n">
         <v>1.29</v>
       </c>
-      <c r="BO26" t="n">
+      <c r="BO29" t="n">
         <v>4.26</v>
       </c>
-      <c r="BP26" t="n">
+      <c r="BP29" t="n">
         <v>1.14</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP29"/>
+  <dimension ref="A1:BP34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ8" t="n">
         <v>2</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ10" t="n">
         <v>2</v>
@@ -2876,7 +2876,7 @@
         <v>3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>3</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR16" t="n">
         <v>0.95</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ17" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>3</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR20" t="n">
         <v>1.77</v>
@@ -5056,7 +5056,7 @@
         <v>3</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR21" t="n">
         <v>1.2</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ22" t="n">
         <v>3</v>
@@ -5489,7 +5489,7 @@
         <v>1</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ23" t="n">
         <v>2</v>
@@ -5928,7 +5928,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR25" t="n">
         <v>1.17</v>
@@ -6876,6 +6876,1096 @@
       </c>
       <c r="BP29" t="n">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8237949</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>45927.5625</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hapoel Katamon</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Maccabi Netanya</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>['74', '88']</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="V30" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X30" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8237945</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>45927.57291666666</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hapoel Petah Tikva</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ironi Tiberias</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>['71', '90+4']</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V31" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X31" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8237947</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>45927.57291666666</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hapoel Tel Aviv</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Hapoel Haifa</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X32" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8237931</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>45927.57291666666</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ironi Kiryat Shmona</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Ashdod</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>['16', '56']</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="V33" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X33" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8237952</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>45927.58333333334</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Maccabi Bnei Raina</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Beitar Jerusalem</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3</v>
+      </c>
+      <c r="N34" t="n">
+        <v>4</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>['18']</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>['45+7', '87', '89']</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V34" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X34" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP34"/>
+  <dimension ref="A1:BP35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ7" t="n">
         <v>2</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ16" t="n">
         <v>1</v>
@@ -4402,7 +4402,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AR18" t="n">
         <v>2.11</v>
@@ -5274,7 +5274,7 @@
         <v>1</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AR22" t="n">
         <v>1.91</v>
@@ -7966,6 +7966,224 @@
       </c>
       <c r="BP34" t="n">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8237934</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>45928.59375</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Bnei Sakhnin</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Maccabi Tel Aviv</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V35" t="n">
+        <v>2</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP35"/>
+  <dimension ref="A1:BP34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2004,7 +2004,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AQ10" t="n">
         <v>2</v>
@@ -5056,7 +5056,7 @@
         <v>3</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AR21" t="n">
         <v>1.2</v>
@@ -5489,7 +5489,7 @@
         <v>1</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AQ23" t="n">
         <v>2</v>
@@ -5793,7 +5793,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>8237944</v>
+        <v>8237935</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -5813,197 +5813,197 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>['32', '38']</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X25" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY25" t="n">
         <v>7</v>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>['52', '75', '87', '90+4', '90+7']</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>['2', '54']</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V25" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X25" t="n">
+      <c r="AZ25" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB25" t="n">
         <v>6</v>
       </c>
-      <c r="Y25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AE25" t="n">
+      <c r="BC25" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="BG25" t="n">
         <v>1.28</v>
       </c>
-      <c r="AF25" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD25" t="n">
+      <c r="BH25" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="BI25" t="n">
         <v>1.56</v>
       </c>
-      <c r="BE25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>1.7</v>
-      </c>
       <c r="BJ25" t="n">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="BK25" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="BL25" t="n">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="BM25" t="n">
-        <v>2.85</v>
+        <v>2.49</v>
       </c>
       <c r="BN25" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="BO25" t="n">
-        <v>4.06</v>
+        <v>3.41</v>
       </c>
       <c r="BP25" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="26">
@@ -6229,7 +6229,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>8237935</v>
+        <v>8237944</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -6249,197 +6249,197 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>['32', '38']</t>
+          <t>['52', '75', '87', '90+4', '90+7']</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['2', '54']</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="R27" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="S27" t="n">
-        <v>6.28</v>
+        <v>4.75</v>
       </c>
       <c r="T27" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="U27" t="n">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="V27" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="W27" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="X27" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AD27" t="n">
-        <v>13.9</v>
+        <v>8.9</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AF27" t="n">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="AG27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AT27" t="n">
         <v>1.68</v>
       </c>
-      <c r="AH27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AL27" t="n">
+      <c r="AU27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="BP27" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="BI27" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BJ27" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BK27" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BM27" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="BN27" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BO27" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="BP27" t="n">
-        <v>1.23</v>
       </c>
     </row>
     <row r="28">
@@ -7101,7 +7101,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>8237945</v>
+        <v>8237931</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -7121,197 +7121,197 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
         <v>2</v>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>['71', '90+4']</t>
+          <t>['16', '56']</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>2.29</v>
+        <v>2.74</v>
       </c>
       <c r="R31" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="S31" t="n">
-        <v>4.94</v>
+        <v>3.7</v>
       </c>
       <c r="T31" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="U31" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="V31" t="n">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="W31" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="X31" t="n">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AC31" t="n">
         <v>1.01</v>
       </c>
       <c r="AD31" t="n">
-        <v>12.4</v>
+        <v>11.2</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF31" t="n">
-        <v>3.52</v>
+        <v>3.36</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AM31" t="n">
-        <v>2.05</v>
+        <v>1.59</v>
       </c>
       <c r="AN31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO31" t="n">
         <v>1.5</v>
       </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
       <c r="AP31" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.89</v>
+        <v>1.38</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.42</v>
+        <v>3.12</v>
       </c>
       <c r="AU31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX31" t="n">
         <v>5</v>
       </c>
-      <c r="AW31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX31" t="n">
+      <c r="AY31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA31" t="n">
         <v>6</v>
       </c>
-      <c r="AY31" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>9</v>
-      </c>
       <c r="BB31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BC31" t="n">
         <v>10</v>
       </c>
       <c r="BD31" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BN31" t="n">
         <v>1.35</v>
       </c>
-      <c r="BE31" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BH31" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="BI31" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BJ31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BK31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BL31" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BM31" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BN31" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BO31" t="n">
-        <v>4.08</v>
+        <v>3.96</v>
       </c>
       <c r="BP31" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="32">
@@ -7537,7 +7537,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>8237931</v>
+        <v>8237945</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -7557,197 +7557,197 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>2</v>
       </c>
       <c r="N33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>['16', '56']</t>
+          <t>['71', '90+4']</t>
         </is>
       </c>
       <c r="Q33" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V33" t="n">
         <v>2.74</v>
       </c>
-      <c r="R33" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="V33" t="n">
-        <v>2.83</v>
-      </c>
       <c r="W33" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="X33" t="n">
-        <v>6.25</v>
+        <v>6.7</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AC33" t="n">
         <v>1.01</v>
       </c>
       <c r="AD33" t="n">
-        <v>11.2</v>
+        <v>12.4</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF33" t="n">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.59</v>
+        <v>2.05</v>
       </c>
       <c r="AN33" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.38</v>
+        <v>0.89</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.12</v>
+        <v>2.42</v>
       </c>
       <c r="AU33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AX33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY33" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ33" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA33" t="n">
         <v>9</v>
       </c>
-      <c r="BA33" t="n">
-        <v>6</v>
-      </c>
       <c r="BB33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BC33" t="n">
         <v>10</v>
       </c>
       <c r="BD33" t="n">
-        <v>2.12</v>
+        <v>1.35</v>
       </c>
       <c r="BE33" t="n">
-        <v>6.89</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="BF33" t="n">
-        <v>2.12</v>
+        <v>4.62</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="BH33" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="BI33" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BJ33" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="BK33" t="n">
-        <v>2.51</v>
+        <v>2.15</v>
       </c>
       <c r="BL33" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="BM33" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="BN33" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO33" t="n">
-        <v>3.96</v>
+        <v>4.08</v>
       </c>
       <c r="BP33" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="34">
@@ -7755,7 +7755,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>8237952</v>
+        <v>8237934</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -7768,421 +7768,203 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>45927.58333333334</v>
+        <v>45928.59375</v>
       </c>
       <c r="F34" t="n">
         <v>5</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>['18']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>['45+7', '87', '89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>4.62</v>
+        <v>10.5</v>
       </c>
       <c r="R34" t="n">
-        <v>2.28</v>
+        <v>2.81</v>
       </c>
       <c r="S34" t="n">
-        <v>2.13</v>
+        <v>1.49</v>
       </c>
       <c r="T34" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="U34" t="n">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="V34" t="n">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="W34" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="X34" t="n">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.75</v>
+        <v>9.6</v>
       </c>
       <c r="AA34" t="n">
-        <v>4</v>
+        <v>6.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.58</v>
+        <v>1.18</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AD34" t="n">
-        <v>14.3</v>
+        <v>19</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AF34" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK34" t="n">
         <v>4.1</v>
       </c>
-      <c r="AG34" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AL34" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AN34" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AP34" t="n">
         <v>0.33</v>
       </c>
       <c r="AQ34" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.34</v>
+        <v>0.86</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.38</v>
+        <v>3.09</v>
       </c>
       <c r="AU34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AX34" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AY34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AZ34" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="BA34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.12</v>
+        <v>8.1</v>
       </c>
       <c r="BE34" t="n">
-        <v>8.050000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="BH34" t="n">
-        <v>2.7</v>
+        <v>3.21</v>
       </c>
       <c r="BI34" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="BJ34" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="BK34" t="n">
-        <v>2.56</v>
+        <v>1.89</v>
       </c>
       <c r="BL34" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="BM34" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="BN34" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="BO34" t="n">
-        <v>4.07</v>
+        <v>3.28</v>
       </c>
       <c r="BP34" t="n">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="n">
-        <v>8237934</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Israel Israeli Premier League</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>45928.59375</v>
-      </c>
-      <c r="F35" t="n">
-        <v>5</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Bnei Sakhnin</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Maccabi Tel Aviv</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="R35" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U35" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="V35" t="n">
-        <v>2</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X35" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BH35" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="BI35" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BJ35" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BK35" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BL35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BM35" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BN35" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BO35" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="BP35" t="n">
         <v>1.25</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -5357,7 +5357,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>8237942</v>
+        <v>8237943</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -5377,197 +5377,197 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
         <v>7</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>['71']</t>
+          <t>['1', '49']</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>['31', '39', '42', '79', '85', '89']</t>
+          <t>['7', '13', '29', '42', '77']</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>3.28</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="S23" t="n">
-        <v>2.9</v>
+        <v>2.29</v>
       </c>
       <c r="T23" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="U23" t="n">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="V23" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="W23" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="X23" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.81</v>
+        <v>4.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.38</v>
+        <v>3.98</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.23</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
         <v>1.01</v>
       </c>
       <c r="AD23" t="n">
-        <v>8.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AF23" t="n">
-        <v>3.35</v>
+        <v>4.25</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AL23" t="n">
         <v>1.25</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AN23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>1</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
         <v>2</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.36</v>
+        <v>1.87</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.56</v>
+        <v>3.54</v>
       </c>
       <c r="AU23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB23" t="n">
         <v>4</v>
       </c>
-      <c r="AV23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>7</v>
-      </c>
       <c r="BC23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD23" t="n">
-        <v>2.14</v>
+        <v>2.84</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.85</v>
+        <v>6.93</v>
       </c>
       <c r="BF23" t="n">
-        <v>2.14</v>
+        <v>1.73</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="BH23" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="BJ23" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="BK23" t="n">
-        <v>2.71</v>
+        <v>2.44</v>
       </c>
       <c r="BL23" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="BM23" t="n">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="BN23" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BO23" t="n">
-        <v>5.27</v>
+        <v>5.05</v>
       </c>
       <c r="BP23" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="24">
@@ -5575,7 +5575,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>8237943</v>
+        <v>8237942</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -5595,197 +5595,197 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N24" t="n">
         <v>7</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>['1', '49']</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>['7', '13', '29', '42', '77']</t>
+          <t>['31', '39', '42', '79', '85', '89']</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>4.2</v>
+        <v>3.28</v>
       </c>
       <c r="R24" t="n">
-        <v>2.29</v>
+        <v>2.05</v>
       </c>
       <c r="S24" t="n">
-        <v>2.29</v>
+        <v>2.9</v>
       </c>
       <c r="T24" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="U24" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="V24" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="W24" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.5</v>
+        <v>2.81</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.98</v>
+        <v>3.38</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>2.23</v>
       </c>
       <c r="AC24" t="n">
         <v>1.01</v>
       </c>
       <c r="AD24" t="n">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AF24" t="n">
-        <v>4.25</v>
+        <v>3.35</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL24" t="n">
         <v>1.25</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO24" t="n">
         <v>1</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ24" t="n">
         <v>2</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.87</v>
+        <v>1.36</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.54</v>
+        <v>2.56</v>
       </c>
       <c r="AU24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC24" t="n">
         <v>8</v>
       </c>
-      <c r="AW24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>6</v>
-      </c>
       <c r="BD24" t="n">
-        <v>2.84</v>
+        <v>2.14</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.93</v>
+        <v>5.85</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.73</v>
+        <v>2.14</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="BH24" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="BK24" t="n">
-        <v>2.44</v>
+        <v>2.71</v>
       </c>
       <c r="BL24" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="BM24" t="n">
-        <v>3.38</v>
+        <v>3.8</v>
       </c>
       <c r="BN24" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BO24" t="n">
-        <v>5.05</v>
+        <v>5.27</v>
       </c>
       <c r="BP24" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="25">
@@ -5793,7 +5793,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>8237935</v>
+        <v>8237944</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -5813,197 +5813,197 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>['32', '38']</t>
+          <t>['52', '75', '87', '90+4', '90+7']</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['2', '54']</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="R25" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="S25" t="n">
-        <v>6.28</v>
+        <v>4.75</v>
       </c>
       <c r="T25" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="U25" t="n">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="V25" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="W25" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="X25" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="AB25" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AD25" t="n">
-        <v>13.9</v>
+        <v>8.9</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AF25" t="n">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="AG25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AT25" t="n">
         <v>1.68</v>
       </c>
-      <c r="AH25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AL25" t="n">
+      <c r="AU25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="BP25" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>1.23</v>
       </c>
     </row>
     <row r="26">
@@ -6229,7 +6229,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>8237944</v>
+        <v>8237935</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -6249,197 +6249,197 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>['32', '38']</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X27" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY27" t="n">
         <v>7</v>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>['52', '75', '87', '90+4', '90+7']</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>['2', '54']</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U27" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V27" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X27" t="n">
+      <c r="AZ27" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB27" t="n">
         <v>6</v>
       </c>
-      <c r="Y27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AE27" t="n">
+      <c r="BC27" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="BG27" t="n">
         <v>1.28</v>
       </c>
-      <c r="AF27" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD27" t="n">
+      <c r="BH27" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="BI27" t="n">
         <v>1.56</v>
       </c>
-      <c r="BE27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BI27" t="n">
-        <v>1.7</v>
-      </c>
       <c r="BJ27" t="n">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="BK27" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="BL27" t="n">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="BM27" t="n">
-        <v>2.85</v>
+        <v>2.49</v>
       </c>
       <c r="BN27" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="BO27" t="n">
-        <v>4.06</v>
+        <v>3.41</v>
       </c>
       <c r="BP27" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="28">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -5793,7 +5793,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>8237944</v>
+        <v>8291603</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -5813,197 +5813,197 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>['70', '90+4']</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>['67']</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AU25" t="n">
         <v>5</v>
       </c>
-      <c r="M25" t="n">
-        <v>2</v>
-      </c>
-      <c r="N25" t="n">
-        <v>7</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>['52', '75', '87', '90+4', '90+7']</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>['2', '54']</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V25" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X25" t="n">
+      <c r="AV25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX25" t="n">
         <v>6</v>
       </c>
-      <c r="Y25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV25" t="n">
+      <c r="AY25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA25" t="n">
         <v>6</v>
       </c>
-      <c r="AW25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>10</v>
-      </c>
       <c r="BB25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BC25" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BH25" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BJ25" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="BK25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BL25" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BM25" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="BN25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BO25" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="BP25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -6011,7 +6011,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>8291603</v>
+        <v>8237935</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -6031,22 +6031,22 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
         <v>2</v>
@@ -6059,169 +6059,169 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>['70', '90+4']</t>
+          <t>['32', '38']</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AN26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ26" t="n">
         <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.97</v>
+        <v>0.8</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.19</v>
+        <v>0.84</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.16</v>
+        <v>1.64</v>
       </c>
       <c r="AU26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV26" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AW26" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AX26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB26" t="n">
         <v>6</v>
       </c>
-      <c r="AY26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>3</v>
-      </c>
       <c r="BC26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BH26" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="BI26" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BK26" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BL26" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BM26" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="BN26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BO26" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="BP26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="27">
@@ -6229,7 +6229,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>8237935</v>
+        <v>8237944</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -6249,197 +6249,197 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>['32', '38']</t>
+          <t>['52', '75', '87', '90+4', '90+7']</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['2', '54']</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="R27" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="S27" t="n">
-        <v>6.28</v>
+        <v>4.75</v>
       </c>
       <c r="T27" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="U27" t="n">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="V27" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="W27" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="X27" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AD27" t="n">
-        <v>13.9</v>
+        <v>8.9</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AF27" t="n">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="AG27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AT27" t="n">
         <v>1.68</v>
       </c>
-      <c r="AH27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AL27" t="n">
+      <c r="AU27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="BP27" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="BI27" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BJ27" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BK27" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BM27" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="BN27" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BO27" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="BP27" t="n">
-        <v>1.23</v>
       </c>
     </row>
     <row r="28">
@@ -7101,7 +7101,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>8237931</v>
+        <v>8237945</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -7121,197 +7121,197 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>2</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>['16', '56']</t>
+          <t>['71', '90+4']</t>
         </is>
       </c>
       <c r="Q31" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V31" t="n">
         <v>2.74</v>
       </c>
-      <c r="R31" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="V31" t="n">
-        <v>2.83</v>
-      </c>
       <c r="W31" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="X31" t="n">
-        <v>6.25</v>
+        <v>6.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AC31" t="n">
         <v>1.01</v>
       </c>
       <c r="AD31" t="n">
-        <v>11.2</v>
+        <v>12.4</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF31" t="n">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.59</v>
+        <v>2.05</v>
       </c>
       <c r="AN31" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.38</v>
+        <v>0.89</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.12</v>
+        <v>2.42</v>
       </c>
       <c r="AU31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AX31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY31" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ31" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA31" t="n">
         <v>9</v>
       </c>
-      <c r="BA31" t="n">
-        <v>6</v>
-      </c>
       <c r="BB31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BC31" t="n">
         <v>10</v>
       </c>
       <c r="BD31" t="n">
-        <v>2.12</v>
+        <v>1.35</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.89</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="BF31" t="n">
-        <v>2.12</v>
+        <v>4.62</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="BH31" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="BI31" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BJ31" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="BK31" t="n">
-        <v>2.51</v>
+        <v>2.15</v>
       </c>
       <c r="BL31" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="BM31" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="BN31" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO31" t="n">
-        <v>3.96</v>
+        <v>4.08</v>
       </c>
       <c r="BP31" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="32">
@@ -7319,7 +7319,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>8237947</v>
+        <v>8237931</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -7339,197 +7339,197 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '56']</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>2.22</v>
+        <v>2.74</v>
       </c>
       <c r="R32" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="S32" t="n">
-        <v>4.02</v>
+        <v>3.7</v>
       </c>
       <c r="T32" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="U32" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="V32" t="n">
-        <v>2.57</v>
+        <v>2.83</v>
       </c>
       <c r="W32" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="X32" t="n">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="Y32" t="n">
         <v>1.06</v>
       </c>
       <c r="Z32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI32" t="n">
         <v>1.7</v>
       </c>
-      <c r="AA32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AJ32" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.97</v>
+        <v>1.59</v>
       </c>
       <c r="AN32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO32" t="n">
         <v>1.5</v>
       </c>
       <c r="AP32" t="n">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.15</v>
+        <v>1.74</v>
       </c>
       <c r="AS32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD32" t="n">
         <v>2.12</v>
       </c>
-      <c r="AT32" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>30</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>1.54</v>
-      </c>
       <c r="BE32" t="n">
-        <v>7.44</v>
+        <v>6.89</v>
       </c>
       <c r="BF32" t="n">
-        <v>3.48</v>
+        <v>2.12</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="BH32" t="n">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
       <c r="BI32" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="BJ32" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="BK32" t="n">
-        <v>2.84</v>
+        <v>2.51</v>
       </c>
       <c r="BL32" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="BM32" t="n">
-        <v>3.16</v>
+        <v>2.8</v>
       </c>
       <c r="BN32" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="BO32" t="n">
-        <v>4.64</v>
+        <v>3.96</v>
       </c>
       <c r="BP32" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="33">
@@ -7537,7 +7537,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>8237945</v>
+        <v>8237947</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -7575,179 +7575,179 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>['71', '90+4']</t>
-        </is>
-      </c>
       <c r="Q33" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="R33" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="S33" t="n">
-        <v>4.94</v>
+        <v>4.02</v>
       </c>
       <c r="T33" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="U33" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="V33" t="n">
-        <v>2.74</v>
+        <v>2.57</v>
       </c>
       <c r="W33" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="X33" t="n">
-        <v>6.7</v>
+        <v>6.15</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AD33" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="AE33" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AK33" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.26</v>
       </c>
       <c r="AL33" t="n">
         <v>1.25</v>
       </c>
       <c r="AM33" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AN33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO33" t="n">
         <v>1.5</v>
       </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
       <c r="AP33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AQ33" t="n">
         <v>1</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.89</v>
+        <v>2.12</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.42</v>
+        <v>3.27</v>
       </c>
       <c r="AU33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AW33" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="AX33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AY33" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="AZ33" t="n">
         <v>11</v>
       </c>
       <c r="BA33" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BB33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BC33" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="BE33" t="n">
-        <v>8.449999999999999</v>
+        <v>7.44</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.62</v>
+        <v>3.48</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="BH33" t="n">
-        <v>2.69</v>
+        <v>2.49</v>
       </c>
       <c r="BI33" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="BJ33" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="BK33" t="n">
-        <v>2.15</v>
+        <v>2.84</v>
       </c>
       <c r="BL33" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="BM33" t="n">
-        <v>2.86</v>
+        <v>3.16</v>
       </c>
       <c r="BN33" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="BO33" t="n">
-        <v>4.08</v>
+        <v>4.64</v>
       </c>
       <c r="BP33" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="34">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Israel Israeli Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP34"/>
+  <dimension ref="A1:BP36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,7 +779,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>8237909</v>
+        <v>8319166</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>8237910</v>
+        <v>8319272</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>8237911</v>
+        <v>8319279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1235,35 +1235,35 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>['28', '51', '69', '77']</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1272,73 +1272,73 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>2.15</v>
+        <v>3.11</v>
       </c>
       <c r="R4" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
-        <v>4.75</v>
+        <v>3.46</v>
       </c>
       <c r="T4" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="U4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AA4" t="n">
         <v>3.3</v>
       </c>
-      <c r="V4" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AB4" t="n">
-        <v>5.63</v>
+        <v>2.9</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>9.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.21</v>
+        <v>1.82</v>
       </c>
       <c r="AI4" t="n">
         <v>1.72</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.5</v>
+        <v>1.41</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1362,64 +1362,64 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV4" t="n">
         <v>2</v>
       </c>
       <c r="AW4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AX4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BA4" t="n">
         <v>7</v>
       </c>
       <c r="BB4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.38</v>
+        <v>2.23</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.78</v>
+        <v>2.05</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="BK4" t="n">
-        <v>2.64</v>
+        <v>3.58</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="BM4" t="n">
         <v>3.98</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BO4" t="n">
         <v>6.18</v>
@@ -1433,7 +1433,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>8237912</v>
+        <v>8319167</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1453,35 +1453,35 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>['54']</t>
+          <t>['28', '51', '69', '77']</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1490,73 +1490,73 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>3.11</v>
+        <v>2.15</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S5" t="n">
-        <v>3.46</v>
+        <v>4.75</v>
       </c>
       <c r="T5" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="U5" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="V5" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="W5" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.73</v>
+        <v>1.49</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.9</v>
+        <v>5.63</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AD5" t="n">
-        <v>9.25</v>
+        <v>10</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AF5" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.82</v>
+        <v>2.21</v>
       </c>
       <c r="AI5" t="n">
         <v>1.72</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.41</v>
+        <v>2.5</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1580,64 +1580,64 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX5" t="n">
         <v>4</v>
       </c>
-      <c r="AV5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>8</v>
-      </c>
       <c r="AY5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA5" t="n">
         <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.23</v>
+        <v>1.38</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.05</v>
+        <v>3.78</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.58</v>
+        <v>2.64</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="BM5" t="n">
         <v>3.98</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BO5" t="n">
         <v>6.18</v>
@@ -1651,7 +1651,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>8291602</v>
+        <v>8319237</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>8237908</v>
+        <v>8319162</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2087,7 +2087,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>8238085</v>
+        <v>8319235</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2174,10 +2174,10 @@
         <v>2.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2192,10 +2192,10 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>8238082</v>
+        <v>8319239</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2325,110 +2325,110 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>['8', '45+1']</t>
+          <t>['37', '58']</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>['48', '90+4']</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="S9" t="n">
-        <v>3.35</v>
+        <v>2.33</v>
       </c>
       <c r="T9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W9" t="n">
         <v>1.4</v>
       </c>
-      <c r="U9" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.39</v>
-      </c>
       <c r="X9" t="n">
-        <v>6.8</v>
+        <v>6.65</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.34</v>
+        <v>4.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF9" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="n">
         <v>1.85</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.33</v>
+        <v>1.99</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.49</v>
+        <v>1.12</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>2</v>
+        <v>0.33</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2452,70 +2452,70 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX9" t="n">
         <v>9</v>
       </c>
-      <c r="AV9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW9" t="n">
+      <c r="AY9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA9" t="n">
         <v>9</v>
       </c>
-      <c r="AX9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>5</v>
-      </c>
       <c r="BB9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BE9" t="n">
         <v>8</v>
       </c>
-      <c r="BD9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>6.73</v>
-      </c>
       <c r="BF9" t="n">
-        <v>2.5</v>
+        <v>1.61</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="BK9" t="n">
-        <v>3.16</v>
+        <v>2.76</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="BM9" t="n">
-        <v>3.5</v>
+        <v>3.98</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.27</v>
+        <v>6.18</v>
       </c>
       <c r="BP9" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="10">
@@ -2523,7 +2523,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>8238083</v>
+        <v>8319236</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2543,197 +2543,197 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>['37', '58']</t>
+          <t>['8', '45+1']</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>['48', '90+4']</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2</v>
+        <v>3.14</v>
       </c>
       <c r="T10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="V10" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="W10" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
-        <v>6.7</v>
+        <v>6.23</v>
       </c>
       <c r="Y10" t="n">
         <v>1.04</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.4</v>
+        <v>2.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.67</v>
+        <v>2.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AD10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
         <v>9</v>
       </c>
-      <c r="AE10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
+      <c r="AV10" t="n">
         <v>5</v>
       </c>
-      <c r="AV10" t="n">
-        <v>6</v>
-      </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>9</v>
       </c>
-      <c r="AY10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>15</v>
-      </c>
       <c r="BA10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BB10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.42</v>
+        <v>1.95</v>
       </c>
       <c r="BE10" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.55</v>
+        <v>2.34</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="BK10" t="n">
-        <v>2.36</v>
+        <v>3.97</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="BM10" t="n">
-        <v>3.5</v>
+        <v>4.39</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.9</v>
+        <v>6.97</v>
       </c>
       <c r="BP10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="11">
@@ -2741,7 +2741,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>8238084</v>
+        <v>8319241</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2761,197 +2761,197 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>['3', '12']</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X11" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="AC11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
         <v>4</v>
       </c>
-      <c r="L11" t="n">
+      <c r="AV11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>7</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>7</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>['2', '7', '18', '26', '53', '57', '83']</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="S11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="V11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X11" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>37</v>
-      </c>
-      <c r="AZ11" t="n">
+      <c r="BA11" t="n">
         <v>4</v>
       </c>
-      <c r="BA11" t="n">
-        <v>8</v>
-      </c>
       <c r="BB11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BC11" t="n">
         <v>9</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.1</v>
+        <v>1.51</v>
       </c>
       <c r="BE11" t="n">
-        <v>14.5</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.300000000000001</v>
+        <v>3.39</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.22</v>
+        <v>2.51</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="BJ11" t="n">
-        <v>2.32</v>
+        <v>1.92</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.8</v>
+        <v>3.08</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.28</v>
+        <v>3.14</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.04</v>
+        <v>5.15</v>
       </c>
       <c r="BP11" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="12">
@@ -2959,7 +2959,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>8238086</v>
+        <v>8319240</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2979,197 +2979,197 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['2', '7', '18', '26', '53', '57', '83']</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>['3', '12']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>2.5</v>
+        <v>1.56</v>
       </c>
       <c r="R12" t="n">
-        <v>2.05</v>
+        <v>2.87</v>
       </c>
       <c r="S12" t="n">
-        <v>3.94</v>
+        <v>7.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="U12" t="n">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="V12" t="n">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="W12" t="n">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="X12" t="n">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC12" t="n">
         <v>1.02</v>
       </c>
-      <c r="Z12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="AD12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>37</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>4</v>
       </c>
-      <c r="AC12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>7</v>
-      </c>
       <c r="BA12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BB12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BC12" t="n">
         <v>9</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.37</v>
+        <v>1.13</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.199999999999999</v>
+        <v>18.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.45</v>
+        <v>7.55</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="BH12" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM12" t="n">
         <v>2.51</v>
       </c>
-      <c r="BI12" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>3.03</v>
-      </c>
       <c r="BN12" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.39</v>
+        <v>3.2</v>
       </c>
       <c r="BP12" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="13">
@@ -3177,7 +3177,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>8237907</v>
+        <v>8319238</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3234,73 +3234,73 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R13" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="S13" t="n">
-        <v>6.25</v>
+        <v>6.69</v>
       </c>
       <c r="T13" t="n">
         <v>1.19</v>
       </c>
       <c r="U13" t="n">
-        <v>3.42</v>
+        <v>4.1</v>
       </c>
       <c r="V13" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="W13" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="X13" t="n">
-        <v>4.6</v>
+        <v>4.47</v>
       </c>
       <c r="Y13" t="n">
         <v>1.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AA13" t="n">
         <v>5.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.67</v>
+        <v>7.1</v>
       </c>
       <c r="AC13" t="n">
         <v>1.02</v>
       </c>
       <c r="AD13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
         <v>1.12</v>
       </c>
       <c r="AF13" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AG13" t="n">
         <v>1.47</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>1.26</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="BJ13" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BM13" t="n">
         <v>2.44</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="BP13" t="n">
         <v>1.25</v>
@@ -3395,7 +3395,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>8238081</v>
+        <v>8319243</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -3452,73 +3452,73 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="R14" t="n">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="S14" t="n">
         <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="V14" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="W14" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X14" t="n">
-        <v>5.25</v>
+        <v>5.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AB14" t="n">
         <v>2.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AD14" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="AE14" t="n">
         <v>1.17</v>
       </c>
       <c r="AF14" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AG14" t="n">
         <v>1.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -3569,37 +3569,37 @@
         <v>9</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.01</v>
+        <v>7.99</v>
       </c>
       <c r="BF14" t="n">
         <v>2.38</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="BK14" t="n">
-        <v>2.17</v>
+        <v>2.68</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BM14" t="n">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BO14" t="n">
         <v>4.32</v>
@@ -3613,7 +3613,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>8237933</v>
+        <v>8319271</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -3670,13 +3670,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -3697,13 +3697,13 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.07</v>
+        <v>2.37</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3724,10 +3724,10 @@
         <v>1.85</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -3831,7 +3831,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>8237926</v>
+        <v>8319270</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -3894,10 +3894,10 @@
         <v>2.1</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="U16" t="n">
         <v>2.65</v>
@@ -3906,37 +3906,37 @@
         <v>2.87</v>
       </c>
       <c r="W16" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.82</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AD16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AE16" t="n">
         <v>1.36</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AH16" t="n">
         <v>1.7</v>
@@ -3948,13 +3948,13 @@
         <v>1.9</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
@@ -4049,7 +4049,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>8237921</v>
+        <v>8319168</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -4109,10 +4109,10 @@
         <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="S17" t="n">
-        <v>3.54</v>
+        <v>3.74</v>
       </c>
       <c r="T17" t="n">
         <v>1.4</v>
@@ -4121,10 +4121,10 @@
         <v>2.65</v>
       </c>
       <c r="V17" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="W17" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X17" t="n">
         <v>7</v>
@@ -4133,13 +4133,13 @@
         <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.01</v>
+        <v>3.17</v>
       </c>
       <c r="AC17" t="n">
         <v>1.06</v>
@@ -4151,13 +4151,13 @@
         <v>1.37</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AI17" t="n">
         <v>1.8</v>
@@ -4166,13 +4166,13 @@
         <v>2</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AN17" t="n">
         <v>1</v>
@@ -4267,7 +4267,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>8237929</v>
+        <v>8319245</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -4324,13 +4324,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R18" t="n">
         <v>2.62</v>
       </c>
       <c r="S18" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="T18" t="n">
         <v>1.32</v>
@@ -4351,25 +4351,25 @@
         <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.18</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.8</v>
+        <v>5.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AC18" t="n">
         <v>1.02</v>
       </c>
       <c r="AD18" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
         <v>1.18</v>
       </c>
       <c r="AF18" t="n">
-        <v>4.68</v>
+        <v>4.75</v>
       </c>
       <c r="AG18" t="n">
         <v>1.57</v>
@@ -4381,13 +4381,13 @@
         <v>2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AK18" t="n">
         <v>3.6</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
         <v>1.03</v>
@@ -4485,7 +4485,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>8237925</v>
+        <v>8319141</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>2.62</v>
       </c>
       <c r="S19" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="T19" t="n">
         <v>1.29</v>
@@ -4557,7 +4557,7 @@
         <v>3.3</v>
       </c>
       <c r="V19" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="W19" t="n">
         <v>1.53</v>
@@ -4575,13 +4575,13 @@
         <v>5.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AC19" t="n">
         <v>1.01</v>
       </c>
       <c r="AD19" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AE19" t="n">
         <v>1.18</v>
@@ -4593,7 +4593,7 @@
         <v>1.61</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AI19" t="n">
         <v>2.08</v>
@@ -4605,7 +4605,7 @@
         <v>3.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
         <v>1.03</v>
@@ -4703,7 +4703,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>8237920</v>
+        <v>8319244</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -4763,10 +4763,10 @@
         <v>1.93</v>
       </c>
       <c r="R20" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="S20" t="n">
-        <v>5.3</v>
+        <v>4.84</v>
       </c>
       <c r="T20" t="n">
         <v>1.32</v>
@@ -4778,10 +4778,10 @@
         <v>2.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="X20" t="n">
-        <v>5.35</v>
+        <v>4.48</v>
       </c>
       <c r="Y20" t="n">
         <v>1.12</v>
@@ -4790,7 +4790,7 @@
         <v>1.35</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AB20" t="n">
         <v>5.75</v>
@@ -4802,7 +4802,7 @@
         <v>18</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF20" t="n">
         <v>4</v>
@@ -4817,13 +4817,13 @@
         <v>1.74</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AK20" t="n">
         <v>1.2</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
         <v>2.6</v>
@@ -4835,7 +4835,7 @@
         <v>3</v>
       </c>
       <c r="AP20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ20" t="n">
         <v>2</v>
@@ -4877,43 +4877,43 @@
         <v>9</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.9</v>
+        <v>3.66</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="BH20" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="BK20" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="BL20" t="n">
         <v>1.77</v>
       </c>
       <c r="BM20" t="n">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="BP20" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="21">
@@ -4921,7 +4921,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>8237932</v>
+        <v>8319247</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -4978,22 +4978,22 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>3.52</v>
+        <v>3.32</v>
       </c>
       <c r="R21" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="T21" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="U21" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="V21" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="W21" t="n">
         <v>1.42</v>
@@ -5005,25 +5005,25 @@
         <v>1.09</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.26</v>
+        <v>3.41</v>
       </c>
       <c r="AB21" t="n">
         <v>2.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AD21" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.52</v>
+        <v>3.98</v>
       </c>
       <c r="AG21" t="n">
         <v>1.81</v>
@@ -5032,16 +5032,16 @@
         <v>1.91</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="AK21" t="n">
         <v>1.3</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
         <v>1.3</v>
@@ -5056,7 +5056,7 @@
         <v>3</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR21" t="n">
         <v>1.2</v>
@@ -5095,43 +5095,43 @@
         <v>11</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="BE21" t="n">
         <v>6.05</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="BH21" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="BK21" t="n">
-        <v>2.96</v>
+        <v>2.25</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="BM21" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.86</v>
+        <v>5.44</v>
       </c>
       <c r="BP21" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="22">
@@ -5139,7 +5139,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>8291605</v>
+        <v>8319252</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>8237943</v>
+        <v>8319259</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -5417,25 +5417,25 @@
         <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="S23" t="n">
         <v>2.29</v>
       </c>
       <c r="T23" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="U23" t="n">
         <v>3.3</v>
       </c>
       <c r="V23" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="W23" t="n">
         <v>1.53</v>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="Y23" t="n">
         <v>1.1</v>
@@ -5444,10 +5444,10 @@
         <v>4.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
         <v>1.01</v>
@@ -5459,25 +5459,25 @@
         <v>1.2</v>
       </c>
       <c r="AF23" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="AK23" t="n">
         <v>1.2</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
         <v>1.22</v>
@@ -5575,7 +5575,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>8237942</v>
+        <v>8319285</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -5641,10 +5641,10 @@
         <v>2.9</v>
       </c>
       <c r="T24" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="U24" t="n">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="V24" t="n">
         <v>2.8</v>
@@ -5653,19 +5653,19 @@
         <v>1.36</v>
       </c>
       <c r="X24" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AC24" t="n">
         <v>1.01</v>
@@ -5674,28 +5674,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF24" t="n">
         <v>3.35</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AK24" t="n">
         <v>1.25</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
         <v>1.31</v>
@@ -5707,7 +5707,7 @@
         <v>1</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ24" t="n">
         <v>2</v>
@@ -5793,7 +5793,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>8291603</v>
+        <v>8319267</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -5813,22 +5813,22 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
         <v>2</v>
@@ -5841,169 +5841,169 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>['70', '90+4']</t>
+          <t>['32', '38']</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AN25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ25" t="n">
         <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.97</v>
+        <v>0.8</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.19</v>
+        <v>0.84</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.16</v>
+        <v>1.64</v>
       </c>
       <c r="AU25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV25" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AW25" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AX25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB25" t="n">
         <v>6</v>
       </c>
-      <c r="AY25" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>3</v>
-      </c>
       <c r="BC25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BH25" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="BI25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BK25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BL25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BM25" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="BN25" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BO25" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="BP25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="26">
@@ -6011,7 +6011,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>8237935</v>
+        <v>8319246</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -6031,22 +6031,22 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>2</v>
@@ -6059,166 +6059,166 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>['32', '38']</t>
+          <t>['70', '90+4']</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>1.94</v>
+        <v>1.42</v>
       </c>
       <c r="R26" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="S26" t="n">
-        <v>6.28</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="U26" t="n">
-        <v>3.26</v>
+        <v>3.75</v>
       </c>
       <c r="V26" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="W26" t="n">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="X26" t="n">
-        <v>5.75</v>
+        <v>3.98</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.46</v>
+        <v>1.13</v>
       </c>
       <c r="AA26" t="n">
-        <v>4.1</v>
+        <v>9.57</v>
       </c>
       <c r="AB26" t="n">
-        <v>5.2</v>
+        <v>12.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AD26" t="n">
-        <v>13.9</v>
+        <v>23</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF26" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="AH26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI26" t="n">
         <v>2.05</v>
       </c>
-      <c r="AI26" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AJ26" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="AK26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AS26" t="n">
         <v>1.19</v>
       </c>
-      <c r="AL26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0.84</v>
-      </c>
       <c r="AT26" t="n">
-        <v>1.64</v>
+        <v>3.16</v>
       </c>
       <c r="AU26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>8</v>
       </c>
-      <c r="AW26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>16</v>
-      </c>
       <c r="BA26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BB26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BC26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="BE26" t="n">
-        <v>9.25</v>
+        <v>13.25</v>
       </c>
       <c r="BF26" t="n">
-        <v>5.27</v>
+        <v>7.7</v>
       </c>
       <c r="BG26" t="n">
         <v>1.28</v>
       </c>
       <c r="BH26" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="BJ26" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="BK26" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="BL26" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="BM26" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="BN26" t="n">
         <v>1.45</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="BP26" t="n">
         <v>1.23</v>
@@ -6229,7 +6229,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>8237944</v>
+        <v>8319268</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="R27" t="n">
         <v>2.15</v>
@@ -6295,64 +6295,64 @@
         <v>4.75</v>
       </c>
       <c r="T27" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="U27" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="V27" t="n">
-        <v>2.73</v>
+        <v>2.82</v>
       </c>
       <c r="W27" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X27" t="n">
-        <v>6</v>
+        <v>6.23</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AD27" t="n">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="AE27" t="n">
         <v>1.28</v>
       </c>
       <c r="AF27" t="n">
-        <v>3.73</v>
+        <v>3.78</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="AN27" t="n">
         <v>0</v>
@@ -6447,7 +6447,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>8237941</v>
+        <v>8319286</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -6507,37 +6507,37 @@
         <v>1.4</v>
       </c>
       <c r="R28" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="n">
         <v>1.16</v>
       </c>
       <c r="U28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="V28" t="n">
         <v>1.94</v>
       </c>
       <c r="W28" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="X28" t="n">
-        <v>4.15</v>
+        <v>3.71</v>
       </c>
       <c r="Y28" t="n">
         <v>1.18</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AA28" t="n">
-        <v>9.029999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>18.06</v>
+        <v>12</v>
       </c>
       <c r="AC28" t="n">
         <v>1.01</v>
@@ -6546,31 +6546,31 @@
         <v>23</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF28" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>6.52</v>
+        <v>5.7</v>
       </c>
       <c r="AN28" t="n">
         <v>3</v>
@@ -6665,7 +6665,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>8237930</v>
+        <v>8319261</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -6725,10 +6725,10 @@
         <v>4.15</v>
       </c>
       <c r="R29" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="S29" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="T29" t="n">
         <v>1.28</v>
@@ -6740,13 +6740,13 @@
         <v>2.25</v>
       </c>
       <c r="W29" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X29" t="n">
-        <v>5.25</v>
+        <v>5.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Z29" t="n">
         <v>3.7</v>
@@ -6767,28 +6767,28 @@
         <v>1.2</v>
       </c>
       <c r="AF29" t="n">
-        <v>4.33</v>
+        <v>4.64</v>
       </c>
       <c r="AG29" t="n">
         <v>1.61</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.25</v>
+        <v>2.21</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AN29" t="n">
         <v>3</v>
@@ -6883,7 +6883,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>8237949</v>
+        <v>8319273</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -6940,73 +6940,73 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>3.64</v>
+        <v>3.52</v>
       </c>
       <c r="R30" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S30" t="n">
-        <v>2.68</v>
+        <v>2.51</v>
       </c>
       <c r="T30" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U30" t="n">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="V30" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="W30" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="X30" t="n">
-        <v>5.85</v>
+        <v>5.55</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z30" t="n">
         <v>3.04</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AB30" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AD30" t="n">
-        <v>11.7</v>
+        <v>9</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AF30" t="n">
-        <v>3.6</v>
+        <v>4.36</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AH30" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AN30" t="n">
         <v>0</v>
@@ -7057,13 +7057,13 @@
         <v>6</v>
       </c>
       <c r="BD30" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="BE30" t="n">
-        <v>6.83</v>
+        <v>7.78</v>
       </c>
       <c r="BF30" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="BG30" t="n">
         <v>1.41</v>
@@ -7072,28 +7072,28 @@
         <v>2.6</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="BJ30" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="BK30" t="n">
         <v>2.23</v>
       </c>
       <c r="BL30" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="BM30" t="n">
-        <v>2.98</v>
+        <v>3.59</v>
       </c>
       <c r="BN30" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BO30" t="n">
-        <v>4.29</v>
+        <v>5.44</v>
       </c>
       <c r="BP30" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="31">
@@ -7101,7 +7101,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>8237945</v>
+        <v>8319320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -7158,37 +7158,37 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>2.29</v>
+        <v>2.01</v>
       </c>
       <c r="R31" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="S31" t="n">
-        <v>4.94</v>
+        <v>4.4</v>
       </c>
       <c r="T31" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="U31" t="n">
-        <v>2.99</v>
+        <v>3.28</v>
       </c>
       <c r="V31" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="W31" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X31" t="n">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AB31" t="n">
         <v>4.2</v>
@@ -7200,31 +7200,31 @@
         <v>12.4</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AF31" t="n">
-        <v>3.52</v>
+        <v>4.01</v>
       </c>
       <c r="AG31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH31" t="n">
         <v>1.85</v>
       </c>
-      <c r="AH31" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AI31" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AN31" t="n">
         <v>1.5</v>
@@ -7281,37 +7281,37 @@
         <v>8.449999999999999</v>
       </c>
       <c r="BF31" t="n">
-        <v>4.62</v>
+        <v>4.1</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="BH31" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="BI31" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BJ31" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="BK31" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="BL31" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="BM31" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="BN31" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BO31" t="n">
-        <v>4.08</v>
+        <v>4.24</v>
       </c>
       <c r="BP31" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="32">
@@ -7319,7 +7319,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>8237931</v>
+        <v>8319173</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -7339,197 +7339,197 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>['16', '56']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>2.74</v>
+        <v>2.26</v>
       </c>
       <c r="R32" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="S32" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="T32" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="U32" t="n">
-        <v>2.94</v>
+        <v>3.26</v>
       </c>
       <c r="V32" t="n">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="W32" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="X32" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="Y32" t="n">
         <v>1.06</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AB32" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AD32" t="n">
-        <v>11.2</v>
+        <v>9</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF32" t="n">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="AN32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO32" t="n">
         <v>1.5</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AQ32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.74</v>
+        <v>1.15</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.38</v>
+        <v>2.12</v>
       </c>
       <c r="AT32" t="n">
-        <v>3.12</v>
+        <v>3.27</v>
       </c>
       <c r="AU32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AW32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX32" t="n">
         <v>10</v>
       </c>
-      <c r="AX32" t="n">
+      <c r="AY32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB32" t="n">
         <v>5</v>
       </c>
-      <c r="AY32" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>4</v>
-      </c>
       <c r="BC32" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BD32" t="n">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="BE32" t="n">
-        <v>6.89</v>
+        <v>7.44</v>
       </c>
       <c r="BF32" t="n">
-        <v>2.12</v>
+        <v>3.45</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="BH32" t="n">
-        <v>2.74</v>
+        <v>2.49</v>
       </c>
       <c r="BI32" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="BJ32" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="BK32" t="n">
-        <v>2.51</v>
+        <v>2.32</v>
       </c>
       <c r="BL32" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="BM32" t="n">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="BN32" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.96</v>
+        <v>4.64</v>
       </c>
       <c r="BP32" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="33">
@@ -7537,7 +7537,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>8237947</v>
+        <v>8319321</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -7557,197 +7557,197 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '56']</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>2.22</v>
+        <v>2.83</v>
       </c>
       <c r="R33" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="S33" t="n">
-        <v>4.02</v>
+        <v>3.86</v>
       </c>
       <c r="T33" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="U33" t="n">
+        <v>3</v>
+      </c>
+      <c r="V33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X33" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB33" t="n">
         <v>3.1</v>
       </c>
-      <c r="V33" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X33" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AC33" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AD33" t="n">
-        <v>12.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF33" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AK33" t="n">
         <v>1.22</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.97</v>
+        <v>1.65</v>
       </c>
       <c r="AN33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO33" t="n">
         <v>1.5</v>
       </c>
       <c r="AP33" t="n">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.15</v>
+        <v>1.74</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.12</v>
+        <v>1.38</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.27</v>
+        <v>3.12</v>
       </c>
       <c r="AU33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX33" t="n">
         <v>5</v>
       </c>
-      <c r="AV33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX33" t="n">
+      <c r="AY33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC33" t="n">
         <v>10</v>
       </c>
-      <c r="AY33" t="n">
-        <v>30</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>16</v>
-      </c>
       <c r="BD33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BG33" t="n">
         <v>1.54</v>
       </c>
-      <c r="BE33" t="n">
-        <v>7.44</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>1.45</v>
-      </c>
       <c r="BH33" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="BI33" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BJ33" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="BK33" t="n">
-        <v>2.84</v>
+        <v>2.34</v>
       </c>
       <c r="BL33" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BM33" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="BN33" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BO33" t="n">
-        <v>4.64</v>
+        <v>5.15</v>
       </c>
       <c r="BP33" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="34">
@@ -7755,7 +7755,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>8237934</v>
+        <v>8319258</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -7768,204 +7768,640 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>45928.59375</v>
+        <v>45927.58333333334</v>
       </c>
       <c r="F34" t="n">
         <v>5</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+7', '87', '89']</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>10.5</v>
+        <v>4.82</v>
       </c>
       <c r="R34" t="n">
-        <v>2.81</v>
+        <v>2.28</v>
       </c>
       <c r="S34" t="n">
-        <v>1.49</v>
+        <v>2.19</v>
       </c>
       <c r="T34" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="U34" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="V34" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="W34" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="X34" t="n">
-        <v>4.9</v>
+        <v>5.54</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z34" t="n">
-        <v>9.6</v>
+        <v>4.37</v>
       </c>
       <c r="AA34" t="n">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AD34" t="n">
-        <v>19</v>
+        <v>14.3</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AF34" t="n">
-        <v>4.89</v>
+        <v>4.33</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.32</v>
+        <v>1.68</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AK34" t="n">
-        <v>4.1</v>
+        <v>2.12</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO34" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AP34" t="n">
         <v>0.33</v>
       </c>
       <c r="AQ34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8319287</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>45928.59375</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Bnei Sakhnin</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Maccabi Tel Aviv</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V35" t="n">
+        <v>2</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ35" t="n">
         <v>2.33</v>
       </c>
-      <c r="AR34" t="n">
+      <c r="AR35" t="n">
         <v>0.86</v>
       </c>
-      <c r="AS34" t="n">
+      <c r="AS35" t="n">
         <v>2.23</v>
       </c>
-      <c r="AT34" t="n">
+      <c r="AT35" t="n">
         <v>3.09</v>
       </c>
-      <c r="AU34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV34" t="n">
+      <c r="AU35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV35" t="n">
         <v>4</v>
       </c>
-      <c r="AW34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX34" t="n">
+      <c r="AW35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX35" t="n">
         <v>14</v>
       </c>
-      <c r="AY34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ34" t="n">
+      <c r="AY35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ35" t="n">
         <v>18</v>
       </c>
-      <c r="BA34" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB34" t="n">
+      <c r="BA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB35" t="n">
         <v>8</v>
       </c>
-      <c r="BC34" t="n">
+      <c r="BC35" t="n">
         <v>9</v>
       </c>
-      <c r="BD34" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BG34" t="n">
+      <c r="BD35" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BG35" t="n">
         <v>1.26</v>
       </c>
-      <c r="BH34" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="BI34" t="n">
+      <c r="BH35" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="BI35" t="n">
         <v>1.55</v>
       </c>
-      <c r="BJ34" t="n">
+      <c r="BJ35" t="n">
         <v>2.32</v>
       </c>
-      <c r="BK34" t="n">
+      <c r="BK35" t="n">
         <v>1.89</v>
       </c>
-      <c r="BL34" t="n">
+      <c r="BL35" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>8319242</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>45929.60416666666</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Maccabi Haifa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Hapoel Be'er Sheva</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI36" t="n">
         <v>1.8</v>
       </c>
-      <c r="BM34" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BN34" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BO34" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="BP34" t="n">
-        <v>1.25</v>
+      <c r="BJ36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
